--- a/Images for Markdown files database updated 30-06-2026.xlsx
+++ b/Images for Markdown files database updated 30-06-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96282904-7E37-4AE7-8CBE-A1C0994F57FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D63C21F-BA2B-40B3-BFB0-CDDAF74F31D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="562">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -1598,6 +1598,138 @@
   </si>
   <si>
     <t>16.1.24_COS_tech_cards.png</t>
+  </si>
+  <si>
+    <t>CompacOnsite</t>
+  </si>
+  <si>
+    <t>15.2.1</t>
+  </si>
+  <si>
+    <t>15.2.1_CNG_Laser.png</t>
+  </si>
+  <si>
+    <t>15.8.1_CNG_Kfactorboard.png</t>
+  </si>
+  <si>
+    <t>15.8.1</t>
+  </si>
+  <si>
+    <t>15.8.2_CNG_bA.png</t>
+  </si>
+  <si>
+    <t>15.8.2</t>
+  </si>
+  <si>
+    <t>15.8.3_CNG-b.png</t>
+  </si>
+  <si>
+    <t>15.8.3</t>
+  </si>
+  <si>
+    <t>15.8.4_CNG_slave.png</t>
+  </si>
+  <si>
+    <t>15.8.4</t>
+  </si>
+  <si>
+    <t>15.9.1_CNG_regulator.png</t>
+  </si>
+  <si>
+    <t>15.9.1</t>
+  </si>
+  <si>
+    <t>15.9.2_CNG_filter.png</t>
+  </si>
+  <si>
+    <t>15.9.2</t>
+  </si>
+  <si>
+    <t>15.9.3_CNG_piston.png</t>
+  </si>
+  <si>
+    <t>15.9.3</t>
+  </si>
+  <si>
+    <t>15.9.4_CNG_solenoid.png</t>
+  </si>
+  <si>
+    <t>15.9.4</t>
+  </si>
+  <si>
+    <t>15.9.5_CNG_regulator_seal.png</t>
+  </si>
+  <si>
+    <t>15.9.5</t>
+  </si>
+  <si>
+    <t>15.9.6_CNG_isovalve.png</t>
+  </si>
+  <si>
+    <t>15.9.6</t>
+  </si>
+  <si>
+    <t>15.9.7_CNG_KG100.png</t>
+  </si>
+  <si>
+    <t>15.9.7</t>
+  </si>
+  <si>
+    <t>15.9.8_CNG_fuses.png</t>
+  </si>
+  <si>
+    <t>15.9.8</t>
+  </si>
+  <si>
+    <t>15.10.1</t>
+  </si>
+  <si>
+    <t>15.10.1_CNG_adj_nipples.png</t>
+  </si>
+  <si>
+    <t>15.10.2</t>
+  </si>
+  <si>
+    <t>15.10.2_CNG_elect_schematic.png</t>
+  </si>
+  <si>
+    <t>15.10.3</t>
+  </si>
+  <si>
+    <t>15.10.3_CNG_GPIO.png</t>
+  </si>
+  <si>
+    <t>15.10.4</t>
+  </si>
+  <si>
+    <t>15.10.4_CNG_temp_pres.png</t>
+  </si>
+  <si>
+    <t>15.10.5</t>
+  </si>
+  <si>
+    <t>15.10.5_CNG_spare_parts.png</t>
+  </si>
+  <si>
+    <t>15.10.6</t>
+  </si>
+  <si>
+    <t>15.10.6_CNG_modbus_timing.png</t>
+  </si>
+  <si>
+    <t>KG100 Meter</t>
+  </si>
+  <si>
+    <t>17.1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1.0_KG100_meter.png </t>
+  </si>
+  <si>
+    <t>17.1.1</t>
+  </si>
+  <si>
+    <t>17.1.1_KG100_dims.png</t>
   </si>
 </sst>
 </file>
@@ -1739,10 +1871,10 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2077,7 +2209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:G202"/>
+  <dimension ref="A1:G224"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
@@ -4754,197 +4886,499 @@
       <c r="F175" s="5"/>
       <c r="G175" s="5"/>
     </row>
+    <row r="177" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C177" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="D177" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="178" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C178" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D178" t="s">
+        <v>521</v>
+      </c>
+    </row>
     <row r="179" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C179" s="18" t="s">
+      <c r="C179" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D179" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="180" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C180" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D180" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="181" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C181" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D181" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="182" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C182" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D182" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="183" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C183" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D183" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="184" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C184" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D184" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="185" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C185" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D185" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="186" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C186" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D186" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="187" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C187" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D187" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="188" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C188" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D188" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="189" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C189" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D189" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="190" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C190" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D190" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="191" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C191" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D191" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="192" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C192" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D192" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C193" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D193" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C194" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D194" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C195" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D195" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A198" s="4"/>
+      <c r="B198" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="C198" s="18" t="s">
         <v>470</v>
       </c>
-      <c r="D179" s="19" t="s">
+      <c r="D198" s="19" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="180" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C180" s="18" t="s">
+      <c r="E198" s="4"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="5"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A199" s="4"/>
+      <c r="B199" s="5"/>
+      <c r="C199" s="18" t="s">
         <v>471</v>
       </c>
-      <c r="D180" s="19" t="s">
+      <c r="D199" s="19" t="s">
         <v>483</v>
       </c>
-    </row>
-    <row r="181" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C181" s="18" t="s">
+      <c r="E199" s="4"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A200" s="4"/>
+      <c r="B200" s="5"/>
+      <c r="C200" s="18" t="s">
         <v>472</v>
       </c>
-      <c r="D181" s="19" t="s">
+      <c r="D200" s="19" t="s">
         <v>484</v>
       </c>
-    </row>
-    <row r="182" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C182" s="18" t="s">
+      <c r="E200" s="4"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="5"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A201" s="4"/>
+      <c r="B201" s="5"/>
+      <c r="C201" s="18" t="s">
         <v>473</v>
       </c>
-      <c r="D182" s="19" t="s">
+      <c r="D201" s="19" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="183" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C183" s="18" t="s">
+      <c r="E201" s="4"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="5"/>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A202" s="4"/>
+      <c r="B202" s="5"/>
+      <c r="C202" s="18" t="s">
         <v>474</v>
       </c>
-      <c r="D183" s="19" t="s">
+      <c r="D202" s="19" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="184" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C184" s="18" t="s">
+      <c r="E202" s="4"/>
+      <c r="F202" s="5"/>
+      <c r="G202" s="5"/>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A203" s="4"/>
+      <c r="B203" s="5"/>
+      <c r="C203" s="18" t="s">
         <v>475</v>
       </c>
-      <c r="D184" s="19" t="s">
+      <c r="D203" s="19" t="s">
         <v>487</v>
       </c>
-    </row>
-    <row r="185" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C185" s="18" t="s">
+      <c r="E203" s="4"/>
+      <c r="F203" s="5"/>
+      <c r="G203" s="5"/>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A204" s="4"/>
+      <c r="B204" s="5"/>
+      <c r="C204" s="18" t="s">
         <v>476</v>
       </c>
-      <c r="D185" s="19" t="s">
+      <c r="D204" s="19" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="186" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C186" s="18" t="s">
+      <c r="E204" s="4"/>
+      <c r="F204" s="5"/>
+      <c r="G204" s="5"/>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A205" s="4"/>
+      <c r="B205" s="5"/>
+      <c r="C205" s="18" t="s">
         <v>477</v>
       </c>
-      <c r="D186" s="19" t="s">
+      <c r="D205" s="19" t="s">
         <v>489</v>
       </c>
-    </row>
-    <row r="187" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C187" s="18" t="s">
+      <c r="E205" s="4"/>
+      <c r="F205" s="5"/>
+      <c r="G205" s="5"/>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A206" s="4"/>
+      <c r="B206" s="5"/>
+      <c r="C206" s="18" t="s">
         <v>478</v>
       </c>
-      <c r="D187" s="19" t="s">
+      <c r="D206" s="19" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="188" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C188" s="18" t="s">
+      <c r="E206" s="4"/>
+      <c r="F206" s="5"/>
+      <c r="G206" s="5"/>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A207" s="4"/>
+      <c r="B207" s="5"/>
+      <c r="C207" s="18" t="s">
         <v>479</v>
       </c>
-      <c r="D188" s="19" t="s">
+      <c r="D207" s="19" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="189" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C189" s="18" t="s">
+      <c r="E207" s="4"/>
+      <c r="F207" s="5"/>
+      <c r="G207" s="5"/>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A208" s="4"/>
+      <c r="B208" s="5"/>
+      <c r="C208" s="18" t="s">
         <v>480</v>
       </c>
-      <c r="D189" s="19" t="s">
+      <c r="D208" s="19" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="190" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C190" s="18" t="s">
+      <c r="E208" s="4"/>
+      <c r="F208" s="5"/>
+      <c r="G208" s="5"/>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A209" s="4"/>
+      <c r="B209" s="5"/>
+      <c r="C209" s="18" t="s">
         <v>481</v>
       </c>
-      <c r="D190" s="19" t="s">
+      <c r="D209" s="19" t="s">
         <v>493</v>
       </c>
-    </row>
-    <row r="191" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C191" s="18" t="s">
+      <c r="E209" s="4"/>
+      <c r="F209" s="5"/>
+      <c r="G209" s="5"/>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A210" s="4"/>
+      <c r="B210" s="5"/>
+      <c r="C210" s="18" t="s">
         <v>505</v>
       </c>
-      <c r="D191" s="19" t="s">
+      <c r="D210" s="19" t="s">
         <v>494</v>
       </c>
-    </row>
-    <row r="192" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C192" s="18" t="s">
+      <c r="E210" s="4"/>
+      <c r="F210" s="5"/>
+      <c r="G210" s="5"/>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A211" s="4"/>
+      <c r="B211" s="5"/>
+      <c r="C211" s="18" t="s">
         <v>506</v>
       </c>
-      <c r="D192" s="19" t="s">
+      <c r="D211" s="19" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="193" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C193" s="18" t="s">
+      <c r="E211" s="4"/>
+      <c r="F211" s="5"/>
+      <c r="G211" s="5"/>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A212" s="4"/>
+      <c r="B212" s="5"/>
+      <c r="C212" s="18" t="s">
         <v>507</v>
       </c>
-      <c r="D193" s="19" t="s">
+      <c r="D212" s="19" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="194" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C194" s="18" t="s">
+      <c r="E212" s="4"/>
+      <c r="F212" s="5"/>
+      <c r="G212" s="5"/>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A213" s="4"/>
+      <c r="B213" s="5"/>
+      <c r="C213" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="D194" s="19" t="s">
+      <c r="D213" s="19" t="s">
         <v>497</v>
       </c>
-    </row>
-    <row r="195" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C195" s="18" t="s">
+      <c r="E213" s="4"/>
+      <c r="F213" s="5"/>
+      <c r="G213" s="5"/>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A214" s="4"/>
+      <c r="B214" s="5"/>
+      <c r="C214" s="18" t="s">
         <v>509</v>
       </c>
-      <c r="D195" s="19" t="s">
+      <c r="D214" s="19" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="196" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C196" s="18" t="s">
+      <c r="E214" s="4"/>
+      <c r="F214" s="5"/>
+      <c r="G214" s="5"/>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A215" s="4"/>
+      <c r="B215" s="5"/>
+      <c r="C215" s="18" t="s">
         <v>510</v>
       </c>
-      <c r="D196" s="19" t="s">
+      <c r="D215" s="19" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="197" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C197" s="18" t="s">
+      <c r="E215" s="4"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="5"/>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A216" s="4"/>
+      <c r="B216" s="5"/>
+      <c r="C216" s="18" t="s">
         <v>511</v>
       </c>
-      <c r="D197" s="19" t="s">
+      <c r="D216" s="19" t="s">
         <v>500</v>
       </c>
-    </row>
-    <row r="198" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C198" s="18" t="s">
+      <c r="E216" s="4"/>
+      <c r="F216" s="5"/>
+      <c r="G216" s="5"/>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A217" s="4"/>
+      <c r="B217" s="5"/>
+      <c r="C217" s="18" t="s">
         <v>512</v>
       </c>
-      <c r="D198" s="19" t="s">
+      <c r="D217" s="19" t="s">
         <v>501</v>
       </c>
-    </row>
-    <row r="199" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C199" s="18" t="s">
+      <c r="E217" s="4"/>
+      <c r="F217" s="5"/>
+      <c r="G217" s="5"/>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A218" s="4"/>
+      <c r="B218" s="5"/>
+      <c r="C218" s="18" t="s">
         <v>513</v>
       </c>
-      <c r="D199" s="19" t="s">
+      <c r="D218" s="19" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="200" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C200" s="18" t="s">
+      <c r="E218" s="4"/>
+      <c r="F218" s="5"/>
+      <c r="G218" s="5"/>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A219" s="4"/>
+      <c r="B219" s="5"/>
+      <c r="C219" s="18" t="s">
         <v>514</v>
       </c>
-      <c r="D200" s="19" t="s">
+      <c r="D219" s="19" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="201" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C201" s="18" t="s">
+      <c r="E219" s="4"/>
+      <c r="F219" s="5"/>
+      <c r="G219" s="5"/>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A220" s="4"/>
+      <c r="B220" s="5"/>
+      <c r="C220" s="18" t="s">
         <v>515</v>
       </c>
-      <c r="D201" s="19" t="s">
+      <c r="D220" s="19" t="s">
         <v>504</v>
       </c>
-    </row>
-    <row r="202" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C202" s="18" t="s">
+      <c r="E220" s="4"/>
+      <c r="F220" s="5"/>
+      <c r="G220" s="5"/>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A221" s="4"/>
+      <c r="B221" s="5"/>
+      <c r="C221" s="18" t="s">
         <v>516</v>
       </c>
-      <c r="D202" s="19" t="s">
+      <c r="D221" s="19" t="s">
         <v>517</v>
       </c>
+      <c r="E221" s="4"/>
+      <c r="F221" s="5"/>
+      <c r="G221" s="5"/>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A223" s="4"/>
+      <c r="B223" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="C223" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="D223" s="19" t="s">
+        <v>559</v>
+      </c>
+      <c r="E223" s="4"/>
+      <c r="F223" s="5"/>
+      <c r="G223" s="5"/>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A224" s="4"/>
+      <c r="B224" s="5"/>
+      <c r="C224" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D224" s="19" t="s">
+        <v>561</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="5"/>
+      <c r="G224" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Images for Markdown files database updated 30-06-2026.xlsx
+++ b/Images for Markdown files database updated 30-06-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D63C21F-BA2B-40B3-BFB0-CDDAF74F31D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79180CE-AC70-488B-8565-67D67F380E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="588">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -1730,6 +1730,84 @@
   </si>
   <si>
     <t>17.1.1_KG100_dims.png</t>
+  </si>
+  <si>
+    <t>18.1.1</t>
+  </si>
+  <si>
+    <t>18.1.2</t>
+  </si>
+  <si>
+    <t>18.1.3</t>
+  </si>
+  <si>
+    <t>18.1.4</t>
+  </si>
+  <si>
+    <t>18.1.5</t>
+  </si>
+  <si>
+    <t>18.2.1</t>
+  </si>
+  <si>
+    <t>Sensors with built-in Transmitter</t>
+  </si>
+  <si>
+    <t>Sensor with External Transmitter</t>
+  </si>
+  <si>
+    <t>18.2.2</t>
+  </si>
+  <si>
+    <t>18.2.3</t>
+  </si>
+  <si>
+    <t>18.2.4</t>
+  </si>
+  <si>
+    <t>18.2.5</t>
+  </si>
+  <si>
+    <t>Sensor with Fluid Control System</t>
+  </si>
+  <si>
+    <t>18.3.1</t>
+  </si>
+  <si>
+    <t>18.3.2</t>
+  </si>
+  <si>
+    <t>18.3.3</t>
+  </si>
+  <si>
+    <t>18.3.4</t>
+  </si>
+  <si>
+    <t>18.3.5</t>
+  </si>
+  <si>
+    <t>Sensor and transmitter</t>
+  </si>
+  <si>
+    <t>Sensor and transmitter angle view</t>
+  </si>
+  <si>
+    <t>Sensor with external trans display</t>
+  </si>
+  <si>
+    <t>18.2.1_Sensor_and_Transmitter.png</t>
+  </si>
+  <si>
+    <t>18.2.2_Sensor_and_Transmitter_angle.png</t>
+  </si>
+  <si>
+    <t>18.2.3_Sensor_and_Transmitter_display.png</t>
+  </si>
+  <si>
+    <t>Approvals and standards emblems</t>
+  </si>
+  <si>
+    <t>18.2.4_Sensor_and_Transmitter_approvals.png</t>
   </si>
 </sst>
 </file>
@@ -2209,15 +2287,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:G224"/>
+  <dimension ref="A1:G242"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.7265625" customWidth="1"/>
+    <col min="2" max="2" width="30.7265625" customWidth="1"/>
     <col min="3" max="3" width="10.6328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="47.26953125" customWidth="1"/>
     <col min="5" max="5" width="16" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1796875" customWidth="1"/>
+    <col min="6" max="6" width="29.81640625" customWidth="1"/>
     <col min="7" max="7" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5379,6 +5457,233 @@
       <c r="E224" s="4"/>
       <c r="F224" s="5"/>
       <c r="G224" s="5"/>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A226" s="4"/>
+      <c r="B226" s="5" t="s">
+        <v>568</v>
+      </c>
+      <c r="C226" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="D226" s="16" t="s">
+        <v>562</v>
+      </c>
+      <c r="E226" s="4"/>
+      <c r="F226" s="5"/>
+      <c r="G226" s="5"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A227" s="4"/>
+      <c r="B227" s="5"/>
+      <c r="C227" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D227" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="E227" s="4"/>
+      <c r="F227" s="5"/>
+      <c r="G227" s="5"/>
+    </row>
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A228" s="4"/>
+      <c r="B228" s="5"/>
+      <c r="C228" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="D228" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="E228" s="4"/>
+      <c r="F228" s="5"/>
+      <c r="G228" s="5"/>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A229" s="4"/>
+      <c r="B229" s="5"/>
+      <c r="C229" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D229" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="E229" s="4"/>
+      <c r="F229" s="5"/>
+      <c r="G229" s="5"/>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A230" s="4"/>
+      <c r="B230" s="5"/>
+      <c r="C230" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D230" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="E230" s="4"/>
+      <c r="F230" s="5"/>
+      <c r="G230" s="5"/>
+    </row>
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A231" s="4"/>
+      <c r="B231" s="5"/>
+      <c r="C231" s="4"/>
+      <c r="D231" s="5"/>
+      <c r="E231" s="4"/>
+      <c r="F231" s="5"/>
+      <c r="G231" s="5"/>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A232" s="4"/>
+      <c r="B232" s="5" t="s">
+        <v>569</v>
+      </c>
+      <c r="C232" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="D232" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="E232" s="4"/>
+      <c r="F232" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G232" s="5"/>
+    </row>
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A233" s="4"/>
+      <c r="B233" s="5"/>
+      <c r="C233" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="D233" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="E233" s="4"/>
+      <c r="F233" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="G233" s="5"/>
+    </row>
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A234" s="4"/>
+      <c r="B234" s="5"/>
+      <c r="C234" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="D234" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="E234" s="4"/>
+      <c r="F234" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="G234" s="5"/>
+    </row>
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A235" s="4"/>
+      <c r="B235" s="5"/>
+      <c r="C235" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="D235" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="E235" s="4"/>
+      <c r="F235" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="G235" s="5"/>
+    </row>
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A236" s="4"/>
+      <c r="B236" s="5"/>
+      <c r="C236" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D236" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="E236" s="4"/>
+      <c r="F236" s="5"/>
+      <c r="G236" s="5"/>
+    </row>
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A237" s="4"/>
+      <c r="B237" s="5"/>
+      <c r="C237" s="4"/>
+      <c r="D237" s="5"/>
+      <c r="E237" s="4"/>
+      <c r="F237" s="5"/>
+      <c r="G237" s="5"/>
+    </row>
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A238" s="4"/>
+      <c r="B238" s="5" t="s">
+        <v>574</v>
+      </c>
+      <c r="C238" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="D238" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="E238" s="4"/>
+      <c r="F238" s="5"/>
+      <c r="G238" s="5"/>
+    </row>
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A239" s="4"/>
+      <c r="B239" s="5"/>
+      <c r="C239" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D239" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="E239" s="4"/>
+      <c r="F239" s="5"/>
+      <c r="G239" s="5"/>
+    </row>
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A240" s="4"/>
+      <c r="B240" s="5"/>
+      <c r="C240" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D240" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="E240" s="4"/>
+      <c r="F240" s="5"/>
+      <c r="G240" s="5"/>
+    </row>
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A241" s="4"/>
+      <c r="B241" s="5"/>
+      <c r="C241" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="D241" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="E241" s="4"/>
+      <c r="F241" s="5"/>
+      <c r="G241" s="5"/>
+    </row>
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A242" s="4"/>
+      <c r="B242" s="5"/>
+      <c r="C242" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="D242" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="E242" s="4"/>
+      <c r="F242" s="5"/>
+      <c r="G242" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Images for Markdown files database updated 30-06-2026.xlsx
+++ b/Images for Markdown files database updated 30-06-2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A79180CE-AC70-488B-8565-67D67F380E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E14764-2D10-4280-BEF1-04F9F31624BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="679">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -1808,6 +1808,279 @@
   </si>
   <si>
     <t>18.2.4_Sensor_and_Transmitter_approvals.png</t>
+  </si>
+  <si>
+    <t>6.3.2</t>
+  </si>
+  <si>
+    <t>6.3.3</t>
+  </si>
+  <si>
+    <t>6.3.4</t>
+  </si>
+  <si>
+    <t>6.3.5</t>
+  </si>
+  <si>
+    <t>6.3.2_GPIO_Pulse_output_if.png</t>
+  </si>
+  <si>
+    <t>6.3.3_GPIO_Pulse_pullup5v.png</t>
+  </si>
+  <si>
+    <t>6.3.4_GPIO_Pulse_pullup12v.png</t>
+  </si>
+  <si>
+    <t>6.3.5_GPIO_Pulse_pullup24v.png</t>
+  </si>
+  <si>
+    <t>12.7.7</t>
+  </si>
+  <si>
+    <t>12.7.8</t>
+  </si>
+  <si>
+    <t>12.7.9</t>
+  </si>
+  <si>
+    <t>12.7.10</t>
+  </si>
+  <si>
+    <t>12.7.11</t>
+  </si>
+  <si>
+    <t>12.8.1</t>
+  </si>
+  <si>
+    <t>12.8.2</t>
+  </si>
+  <si>
+    <t>12.8.3</t>
+  </si>
+  <si>
+    <t>12.8.4</t>
+  </si>
+  <si>
+    <t>12.8.5</t>
+  </si>
+  <si>
+    <t>12.8.6</t>
+  </si>
+  <si>
+    <t>12.8.7</t>
+  </si>
+  <si>
+    <t>12.8.8</t>
+  </si>
+  <si>
+    <t>12.8.9</t>
+  </si>
+  <si>
+    <t>12.9.1</t>
+  </si>
+  <si>
+    <t>12.9.2</t>
+  </si>
+  <si>
+    <t>12.9.3</t>
+  </si>
+  <si>
+    <t>12.9.4</t>
+  </si>
+  <si>
+    <t>12.9.5</t>
+  </si>
+  <si>
+    <t>12.9.6</t>
+  </si>
+  <si>
+    <t>12.9.7</t>
+  </si>
+  <si>
+    <t>12.9.8</t>
+  </si>
+  <si>
+    <t>12.9.9</t>
+  </si>
+  <si>
+    <t>12.9.10</t>
+  </si>
+  <si>
+    <t>12.9.11</t>
+  </si>
+  <si>
+    <t>12.9.12</t>
+  </si>
+  <si>
+    <t>12.9.13</t>
+  </si>
+  <si>
+    <t>12.9.14</t>
+  </si>
+  <si>
+    <t>12.9.15</t>
+  </si>
+  <si>
+    <t>12.10.1</t>
+  </si>
+  <si>
+    <t>12.10.2</t>
+  </si>
+  <si>
+    <t>12.10.3</t>
+  </si>
+  <si>
+    <t>12.10.4</t>
+  </si>
+  <si>
+    <t>12.10.5</t>
+  </si>
+  <si>
+    <t>12.10.6</t>
+  </si>
+  <si>
+    <t>12.10.7</t>
+  </si>
+  <si>
+    <t>12.10.8</t>
+  </si>
+  <si>
+    <t>12.10.9</t>
+  </si>
+  <si>
+    <t>12.10.10</t>
+  </si>
+  <si>
+    <t>12.10.11</t>
+  </si>
+  <si>
+    <t>12.10.12</t>
+  </si>
+  <si>
+    <t>12.10.13</t>
+  </si>
+  <si>
+    <t>12.11.1</t>
+  </si>
+  <si>
+    <t>12.11.2</t>
+  </si>
+  <si>
+    <t>12.11.3</t>
+  </si>
+  <si>
+    <t>12.11.4</t>
+  </si>
+  <si>
+    <t>12.12.1</t>
+  </si>
+  <si>
+    <t>12.12.2</t>
+  </si>
+  <si>
+    <t>12.12.3</t>
+  </si>
+  <si>
+    <t>12.13.0</t>
+  </si>
+  <si>
+    <t>12.13.1</t>
+  </si>
+  <si>
+    <t>12.13.2</t>
+  </si>
+  <si>
+    <t>12.13.3</t>
+  </si>
+  <si>
+    <t>12.13.4</t>
+  </si>
+  <si>
+    <t>12.13.5</t>
+  </si>
+  <si>
+    <t>12.13.6</t>
+  </si>
+  <si>
+    <t>12.13.7</t>
+  </si>
+  <si>
+    <t>12.13.8</t>
+  </si>
+  <si>
+    <t>12.13.9</t>
+  </si>
+  <si>
+    <t>12.13.10</t>
+  </si>
+  <si>
+    <t>12.13.11</t>
+  </si>
+  <si>
+    <t>12.13.12</t>
+  </si>
+  <si>
+    <t>12.13.13</t>
+  </si>
+  <si>
+    <t>12.13.14</t>
+  </si>
+  <si>
+    <t>12.13.15</t>
+  </si>
+  <si>
+    <t>12.13.16</t>
+  </si>
+  <si>
+    <t>12.13.17</t>
+  </si>
+  <si>
+    <t>12.13.18</t>
+  </si>
+  <si>
+    <t>12.13.19</t>
+  </si>
+  <si>
+    <t>12.13.20</t>
+  </si>
+  <si>
+    <t>12.13.21</t>
+  </si>
+  <si>
+    <t>12.14.1</t>
+  </si>
+  <si>
+    <t>12.14.2</t>
+  </si>
+  <si>
+    <t>12.16.1</t>
+  </si>
+  <si>
+    <t>12.16.2</t>
+  </si>
+  <si>
+    <t>12.16.3</t>
+  </si>
+  <si>
+    <t>12.16.4</t>
+  </si>
+  <si>
+    <t>12.16.5</t>
+  </si>
+  <si>
+    <t>Comfill LITE specific</t>
+  </si>
+  <si>
+    <t>12.99.0</t>
+  </si>
+  <si>
+    <t>12.99.0_LITE_footprint.png</t>
+  </si>
+  <si>
+    <t>12.99.1</t>
+  </si>
+  <si>
+    <t>12.99.1_LITE_layout.png</t>
   </si>
 </sst>
 </file>
@@ -1904,7 +2177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1953,6 +2226,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2287,7 +2563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:G242"/>
+  <dimension ref="A1:G336"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
@@ -3184,10 +3460,10 @@
       <c r="B69" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="12" t="s">
         <v>179</v>
       </c>
       <c r="E69" s="4"/>
@@ -3197,10 +3473,10 @@
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="12" t="s">
         <v>75</v>
       </c>
       <c r="E70" s="4"/>
@@ -3210,10 +3486,10 @@
     <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="4"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="12" t="s">
         <v>79</v>
       </c>
       <c r="E71" s="4"/>
@@ -3223,10 +3499,10 @@
     <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="4"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" s="12" t="s">
         <v>80</v>
       </c>
       <c r="E72" s="4"/>
@@ -3236,10 +3512,10 @@
     <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="4"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D73" s="5" t="s">
+      <c r="D73" s="12" t="s">
         <v>81</v>
       </c>
       <c r="E73" s="4"/>
@@ -3249,10 +3525,10 @@
     <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="4"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="12" t="s">
         <v>82</v>
       </c>
       <c r="E74" s="4"/>
@@ -3262,10 +3538,10 @@
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="4"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="4" t="s">
+      <c r="C75" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D75" s="5" t="s">
+      <c r="D75" s="12" t="s">
         <v>84</v>
       </c>
       <c r="E75" s="4"/>
@@ -3275,10 +3551,10 @@
     <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="4"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="4" t="s">
+      <c r="C76" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="12" t="s">
         <v>169</v>
       </c>
       <c r="E76" s="4"/>
@@ -3288,10 +3564,10 @@
     <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="4"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="4" t="s">
+      <c r="C77" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="D77" s="12" t="s">
         <v>86</v>
       </c>
       <c r="E77" s="4"/>
@@ -3299,26 +3575,26 @@
       <c r="G77" s="5"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="6"/>
-      <c r="B78" s="7"/>
-      <c r="C78" s="6"/>
-      <c r="D78" s="7"/>
-      <c r="E78" s="6"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="13" t="s">
+        <v>588</v>
+      </c>
+      <c r="D78" s="20" t="s">
+        <v>592</v>
+      </c>
+      <c r="E78" s="4"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A79" s="4">
-        <v>7</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>71</v>
+      <c r="A79" s="4"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="13" t="s">
+        <v>589</v>
+      </c>
+      <c r="D79" s="20" t="s">
+        <v>593</v>
       </c>
       <c r="E79" s="4"/>
       <c r="F79" s="5"/>
@@ -3327,11 +3603,11 @@
     <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="4"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>72</v>
+      <c r="C80" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="D80" s="20" t="s">
+        <v>594</v>
       </c>
       <c r="E80" s="4"/>
       <c r="F80" s="5"/>
@@ -3340,11 +3616,11 @@
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="4"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>73</v>
+      <c r="C81" s="13" t="s">
+        <v>591</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>595</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="5"/>
@@ -3361,16 +3637,16 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="5"/>
@@ -3380,10 +3656,10 @@
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="4" t="s">
-        <v>56</v>
+        <v>70</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="5"/>
@@ -3393,62 +3669,62 @@
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="4" t="s">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A86" s="4"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D86" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E86" s="4"/>
+      <c r="A86" s="6"/>
+      <c r="B86" s="7"/>
+      <c r="C86" s="6"/>
+      <c r="D86" s="7"/>
+      <c r="E86" s="6"/>
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A87" s="4"/>
-      <c r="B87" s="5"/>
+      <c r="A87" s="4">
+        <v>8</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>64</v>
+      </c>
       <c r="C87" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A88" s="6"/>
-      <c r="B88" s="7"/>
-      <c r="C88" s="6"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="6"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E88" s="4"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A89" s="4">
-        <v>9</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>266</v>
-      </c>
+      <c r="A89" s="4"/>
+      <c r="B89" s="5"/>
       <c r="C89" s="4" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>150</v>
+        <v>61</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="5"/>
@@ -3458,14 +3734,12 @@
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="4" t="s">
-        <v>264</v>
+        <v>58</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="E90" s="17">
-        <v>46098</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="E90" s="4"/>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
     </row>
@@ -3473,36 +3747,36 @@
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="4" t="s">
-        <v>158</v>
+        <v>54</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A92" s="4"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="E92" s="4"/>
+      <c r="A92" s="6"/>
+      <c r="B92" s="7"/>
+      <c r="C92" s="6"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="6"/>
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A93" s="4"/>
-      <c r="B93" s="5"/>
+      <c r="A93" s="4">
+        <v>9</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>266</v>
+      </c>
       <c r="C93" s="4" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="5"/>
@@ -3512,12 +3786,14 @@
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="4" t="s">
-        <v>161</v>
+        <v>264</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="E94" s="4"/>
+        <v>265</v>
+      </c>
+      <c r="E94" s="17">
+        <v>46098</v>
+      </c>
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
@@ -3525,10 +3801,10 @@
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="4" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="5"/>
@@ -3538,10 +3814,10 @@
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="4" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="5"/>
@@ -3551,10 +3827,10 @@
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="4" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="5"/>
@@ -3563,8 +3839,12 @@
     <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="5"/>
+      <c r="C98" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>166</v>
+      </c>
       <c r="E98" s="4"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
@@ -3572,8 +3852,12 @@
     <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="5"/>
+      <c r="C99" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>168</v>
+      </c>
       <c r="E99" s="4"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
@@ -3581,197 +3865,165 @@
     <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="5"/>
+      <c r="C100" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>177</v>
+      </c>
       <c r="E100" s="4"/>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A101" s="6"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="6"/>
-      <c r="D101" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E101" s="6"/>
+      <c r="A101" s="4"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E101" s="4"/>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
-      <c r="B102" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="C102" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D102" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="E102" s="17">
-        <v>46098</v>
-      </c>
+      <c r="B102" s="5"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="5"/>
+      <c r="E102" s="4"/>
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
-      <c r="C103" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="E103" s="17">
-        <v>46098</v>
-      </c>
+      <c r="C103" s="4"/>
+      <c r="D103" s="5"/>
+      <c r="E103" s="4"/>
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
-      <c r="C104" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="E104" s="17">
-        <v>46098</v>
-      </c>
+      <c r="C104" s="4"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="4"/>
       <c r="F104" s="5"/>
       <c r="G104" s="5"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" s="4"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D105" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="E105" s="17">
-        <v>46098</v>
-      </c>
+      <c r="A105" s="6"/>
+      <c r="B105" s="7"/>
+      <c r="C105" s="6"/>
+      <c r="D105" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E105" s="6"/>
       <c r="F105" s="5"/>
       <c r="G105" s="5"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="4"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="4"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="4"/>
+      <c r="B106" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="E106" s="17">
+        <v>46098</v>
+      </c>
       <c r="F106" s="5"/>
       <c r="G106" s="5"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" s="6"/>
-      <c r="B107" s="7"/>
-      <c r="C107" s="6"/>
-      <c r="D107" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E107" s="6"/>
+      <c r="A107" s="4"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D107" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="E107" s="17">
+        <v>46098</v>
+      </c>
       <c r="F107" s="5"/>
       <c r="G107" s="5"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="4"/>
-      <c r="B108" s="5" t="s">
-        <v>272</v>
-      </c>
+      <c r="B108" s="5"/>
       <c r="C108" s="4" t="s">
-        <v>273</v>
+        <v>183</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="E108" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="G108" s="5" t="s">
-        <v>327</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="4"/>
       <c r="B109" s="5"/>
       <c r="C109" s="4" t="s">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="E109" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F109" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="G109" s="5" t="s">
-        <v>327</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="F109" s="5"/>
+      <c r="G109" s="5"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="4"/>
       <c r="B110" s="5"/>
-      <c r="C110" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="E110" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F110" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="G110" s="5" t="s">
-        <v>327</v>
-      </c>
+      <c r="C110" s="4"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" s="4"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="D111" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="E111" s="17">
-        <v>46099</v>
-      </c>
-      <c r="F111" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="G111" s="5" t="s">
-        <v>327</v>
-      </c>
+      <c r="A111" s="6"/>
+      <c r="B111" s="7"/>
+      <c r="C111" s="6"/>
+      <c r="D111" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E111" s="6"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="4"/>
-      <c r="B112" s="5"/>
+      <c r="B112" s="5" t="s">
+        <v>272</v>
+      </c>
       <c r="C112" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="E112" s="17">
         <v>46099</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G112" s="5" t="s">
         <v>327</v>
@@ -3781,10 +4033,10 @@
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E113" s="17">
         <v>46099</v>
@@ -3800,16 +4052,16 @@
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="4" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E114" s="17">
         <v>46099</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G114" s="5" t="s">
         <v>327</v>
@@ -3819,16 +4071,16 @@
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E115" s="17">
         <v>46099</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="G115" s="5" t="s">
         <v>327</v>
@@ -3838,16 +4090,16 @@
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="4" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E116" s="17">
         <v>46099</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G116" s="5" t="s">
         <v>327</v>
@@ -3857,16 +4109,16 @@
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E117" s="17">
         <v>46099</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="G117" s="5" t="s">
         <v>327</v>
@@ -3876,16 +4128,16 @@
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="4" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E118" s="17">
         <v>46099</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="G118" s="5" t="s">
         <v>327</v>
@@ -3895,16 +4147,16 @@
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="4" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E119" s="17">
         <v>46099</v>
       </c>
       <c r="F119" s="5" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G119" s="5" t="s">
         <v>327</v>
@@ -3914,16 +4166,16 @@
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="4" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="E120" s="17">
         <v>46099</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G120" s="5" t="s">
         <v>327</v>
@@ -3933,16 +4185,16 @@
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="4" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="E121" s="17">
         <v>46099</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="G121" s="5" t="s">
         <v>327</v>
@@ -3952,16 +4204,16 @@
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="4" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="E122" s="17">
         <v>46099</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G122" s="5" t="s">
         <v>327</v>
@@ -3971,16 +4223,16 @@
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="4" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="E123" s="17">
         <v>46099</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="G123" s="5" t="s">
         <v>327</v>
@@ -3990,16 +4242,16 @@
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="4" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="E124" s="17">
         <v>46099</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G124" s="5" t="s">
         <v>327</v>
@@ -4009,16 +4261,16 @@
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="E125" s="17">
         <v>46099</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G125" s="5" t="s">
         <v>327</v>
@@ -4028,16 +4280,16 @@
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="4" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="E126" s="17">
         <v>46099</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="G126" s="5" t="s">
         <v>327</v>
@@ -4047,16 +4299,16 @@
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="4" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="E127" s="17">
         <v>46099</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="G127" s="5" t="s">
         <v>327</v>
@@ -4066,16 +4318,16 @@
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="4" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="E128" s="17">
         <v>46099</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G128" s="5" t="s">
         <v>327</v>
@@ -4085,92 +4337,92 @@
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="4" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>343</v>
+        <v>308</v>
       </c>
       <c r="E129" s="17">
         <v>46099</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>353</v>
+        <v>318</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="4" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>344</v>
+        <v>309</v>
       </c>
       <c r="E130" s="17">
         <v>46099</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>342</v>
+        <v>311</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="4" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="E131" s="17">
         <v>46099</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="4" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>346</v>
+        <v>316</v>
       </c>
       <c r="E132" s="17">
         <v>46099</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="4" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E133" s="17">
         <v>46099</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>342</v>
@@ -4180,16 +4432,16 @@
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="4" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E134" s="17">
         <v>46099</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="G134" s="5" t="s">
         <v>342</v>
@@ -4199,16 +4451,16 @@
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="4" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E135" s="17">
         <v>46099</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>342</v>
@@ -4218,16 +4470,16 @@
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="4" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E136" s="17">
         <v>46099</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G136" s="5" t="s">
         <v>342</v>
@@ -4237,16 +4489,16 @@
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="4" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E137" s="17">
         <v>46099</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G137" s="5" t="s">
         <v>342</v>
@@ -4256,16 +4508,16 @@
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E138" s="17">
         <v>46099</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="G138" s="5" t="s">
         <v>342</v>
@@ -4275,16 +4527,16 @@
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="4" t="s">
-        <v>372</v>
+        <v>338</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="E139" s="17">
         <v>46099</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G139" s="5" t="s">
         <v>342</v>
@@ -4294,16 +4546,16 @@
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="4" t="s">
-        <v>373</v>
+        <v>339</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E140" s="17">
         <v>46099</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="G140" s="5" t="s">
         <v>342</v>
@@ -4313,16 +4565,16 @@
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="4" t="s">
-        <v>374</v>
+        <v>340</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="E141" s="17">
         <v>46099</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>342</v>
@@ -4332,16 +4584,16 @@
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="4" t="s">
-        <v>375</v>
+        <v>341</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="E142" s="17">
         <v>46099</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="G142" s="5" t="s">
         <v>342</v>
@@ -4351,16 +4603,16 @@
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="4" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E143" s="17">
         <v>46099</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>342</v>
@@ -4370,149 +4622,149 @@
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="E144" s="17">
         <v>46099</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>371</v>
+        <v>357</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="4" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="E145" s="17">
         <v>46099</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="E146" s="17">
         <v>46099</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>399</v>
+        <v>366</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="4" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>402</v>
+        <v>370</v>
       </c>
       <c r="E147" s="17">
         <v>46099</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>401</v>
+        <v>367</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>400</v>
+        <v>342</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="4" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>403</v>
+        <v>378</v>
       </c>
       <c r="E148" s="17">
         <v>46099</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="4" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
       <c r="E149" s="17">
         <v>46099</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>416</v>
+        <v>381</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="4" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="E150" s="17">
         <v>46099</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>329</v>
+        <v>399</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>400</v>
+        <v>382</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E151" s="17">
         <v>46099</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>417</v>
+        <v>401</v>
       </c>
       <c r="G151" s="5" t="s">
         <v>400</v>
@@ -4522,16 +4774,16 @@
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="4" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="E152" s="17">
         <v>46099</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>418</v>
+        <v>400</v>
       </c>
       <c r="G152" s="5" t="s">
         <v>400</v>
@@ -4541,16 +4793,16 @@
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="4" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="E153" s="17">
         <v>46099</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="G153" s="5" t="s">
         <v>400</v>
@@ -4560,16 +4812,16 @@
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="4" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E154" s="17">
         <v>46099</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>420</v>
+        <v>329</v>
       </c>
       <c r="G154" s="5" t="s">
         <v>400</v>
@@ -4579,16 +4831,16 @@
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="4" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="E155" s="17">
         <v>46099</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="G155" s="5" t="s">
         <v>400</v>
@@ -4598,16 +4850,16 @@
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="E156" s="17">
         <v>46099</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="G156" s="5" t="s">
         <v>400</v>
@@ -4617,16 +4869,16 @@
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E157" s="17">
         <v>46099</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="G157" s="5" t="s">
         <v>400</v>
@@ -4636,16 +4888,16 @@
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="4" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="E158" s="17">
         <v>46099</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="G158" s="5" t="s">
         <v>400</v>
@@ -4655,16 +4907,16 @@
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="4" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="E159" s="17">
         <v>46099</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="G159" s="5" t="s">
         <v>400</v>
@@ -4674,16 +4926,16 @@
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="4" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E160" s="17">
         <v>46099</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="G160" s="5" t="s">
         <v>400</v>
@@ -4693,92 +4945,92 @@
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="4" t="s">
-        <v>427</v>
+        <v>395</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="E161" s="17">
         <v>46099</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="4" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="E162" s="17">
         <v>46099</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>433</v>
+        <v>424</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="4" t="s">
-        <v>429</v>
+        <v>397</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="E163" s="17">
         <v>46099</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="4" t="s">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>437</v>
+        <v>415</v>
       </c>
       <c r="E164" s="17">
         <v>46099</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>433</v>
+        <v>400</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="4" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="E165" s="17">
         <v>46099</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>433</v>
@@ -4788,16 +5040,16 @@
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="4" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E166" s="17">
         <v>46099</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>444</v>
+        <v>433</v>
       </c>
       <c r="G166" s="5" t="s">
         <v>433</v>
@@ -4807,92 +5059,92 @@
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="4" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>454</v>
+        <v>436</v>
       </c>
       <c r="E167" s="17">
         <v>46099</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="4" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>455</v>
+        <v>437</v>
       </c>
       <c r="E168" s="17">
         <v>46099</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="4" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>456</v>
+        <v>438</v>
       </c>
       <c r="E169" s="17">
         <v>46099</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="4" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>457</v>
+        <v>439</v>
       </c>
       <c r="E170" s="17">
         <v>46099</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="4" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="E171" s="17">
         <v>46099</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="G171" s="5" t="s">
         <v>445</v>
@@ -4902,16 +5154,16 @@
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="4" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="E172" s="17">
         <v>46099</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>445</v>
@@ -4921,16 +5173,16 @@
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="4" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E173" s="17">
         <v>46099</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>445</v>
@@ -4940,16 +5192,16 @@
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="4" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="E174" s="17">
         <v>46099</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G174" s="5" t="s">
         <v>445</v>
@@ -4958,732 +5210,1225 @@
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
-      <c r="C175" s="4"/>
-      <c r="D175" s="5"/>
-      <c r="E175" s="4"/>
-      <c r="F175" s="5"/>
-      <c r="G175" s="5"/>
-    </row>
-    <row r="177" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C177" s="1" t="s">
+      <c r="C175" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D175" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="E175" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F175" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="G175" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A176" s="4"/>
+      <c r="B176" s="5"/>
+      <c r="C176" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="D176" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="E176" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>467</v>
+      </c>
+      <c r="G176" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A177" s="4"/>
+      <c r="B177" s="5"/>
+      <c r="C177" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="D177" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E177" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F177" s="5" t="s">
+        <v>468</v>
+      </c>
+      <c r="G177" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A178" s="4"/>
+      <c r="B178" s="5"/>
+      <c r="C178" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="D178" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="E178" s="17">
+        <v>46099</v>
+      </c>
+      <c r="F178" s="5" t="s">
+        <v>469</v>
+      </c>
+      <c r="G178" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A179" s="4"/>
+      <c r="B179" s="5"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="5"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="5"/>
+      <c r="G179" s="5"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C181" s="1" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C182" s="1" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C183" s="1" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C184" s="1" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C185" s="1" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C186" s="1" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C187" s="1" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C188" s="1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C189" s="1" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C190" s="1" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C191" s="1" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="C192" s="1" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="193" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C193" s="1" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="194" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C194" s="1" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="195" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C195" s="1" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="196" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C196" s="1" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="197" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C197" s="1" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="198" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C198" s="1" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="199" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C199" s="1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="200" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C200" s="1" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="201" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C201" s="1" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="202" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C202" s="1" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="203" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C203" s="1" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="204" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C204" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="205" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C205" s="1" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="206" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C206" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="207" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C207" s="1" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="208" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C208" s="1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="209" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C209" s="1" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="210" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C210" s="1" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="211" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C211" s="1" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="212" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C212" s="1" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="213" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C213" s="1" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="214" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C214" s="1" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="215" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C215" s="1" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="216" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C216" s="1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="217" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C217" s="1" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="218" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C218" s="1" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="219" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C219" s="1" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="220" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C220" s="1" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="221" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C221" s="1" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="222" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C222" s="1" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="223" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C223" s="1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="224" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C224" s="1" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="225" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C225" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="226" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C226" s="1" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="227" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C227" s="1" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="228" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C228" s="1" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="229" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C229" s="1" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="230" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C230" s="1" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="231" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C231" s="1" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="232" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C232" s="1" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="233" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C233" s="1" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="234" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C234" s="1" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="235" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C235" s="1" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="236" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C236" s="1" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="237" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C237" s="1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="238" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C238" s="1" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="239" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C239" s="1" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="240" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C240" s="1" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="241" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C241" s="1" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="242" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C242" s="1" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="243" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C243" s="1" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="244" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C244" s="1" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="245" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C245" s="1" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="246" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C246" s="1" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="247" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C247" s="1" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="248" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C248" s="1" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="249" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C249" s="1" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="250" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C250" s="1" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="251" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C251" s="1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="252" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C252" s="1" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="253" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C253" s="1" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="254" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C254" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="255" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C255" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="256" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="C256" s="1" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="257" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C257" s="1" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="258" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C258" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="260" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B260" t="s">
+        <v>674</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="D260" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="261" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C261" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="D261" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="270" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C270" s="1" t="s">
         <v>519</v>
       </c>
-      <c r="D177" t="s">
+    </row>
+    <row r="271" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C271" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D271" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="178" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C178" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="D178" t="s">
+    <row r="272" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="C272" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="D272" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="179" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C179" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="D179" t="s">
+    <row r="273" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C273" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="D273" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="180" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C180" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="D180" t="s">
+    <row r="274" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C274" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D274" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="181" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C181" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="D181" t="s">
+    <row r="275" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C275" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D275" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="182" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C182" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="D182" t="s">
+    <row r="276" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C276" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D276" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="183" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C183" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="D183" t="s">
+    <row r="277" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C277" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D277" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="184" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C184" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="D184" t="s">
+    <row r="278" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C278" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D278" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="185" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C185" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="D185" t="s">
+    <row r="279" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C279" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D279" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="186" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C186" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="D186" t="s">
+    <row r="280" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C280" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D280" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="187" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C187" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="D187" t="s">
+    <row r="281" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C281" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D281" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="188" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C188" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="D188" t="s">
+    <row r="282" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C282" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D282" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="189" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C189" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="D189" t="s">
+    <row r="283" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C283" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D283" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="190" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C190" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="D190" t="s">
+    <row r="284" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C284" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D284" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="191" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C191" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="D191" t="s">
+    <row r="285" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C285" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D285" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="192" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C192" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="D192" t="s">
+    <row r="286" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C286" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D286" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C193" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="D193" t="s">
+    <row r="287" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C287" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D287" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C194" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D194" t="s">
+    <row r="288" spans="3:4" x14ac:dyDescent="0.35">
+      <c r="C288" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D288" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="C195" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="D195" t="s">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D289" t="s">
         <v>556</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A198" s="4"/>
-      <c r="B198" s="5" t="s">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A291" s="4"/>
+      <c r="B291" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="C198" s="18" t="s">
+      <c r="C291" s="18" t="s">
         <v>470</v>
       </c>
-      <c r="D198" s="19" t="s">
+      <c r="E291" s="4"/>
+      <c r="F291" s="5"/>
+      <c r="G291" s="5"/>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A292" s="4"/>
+      <c r="B292" s="5"/>
+      <c r="C292" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="D292" s="19" t="s">
         <v>482</v>
       </c>
-      <c r="E198" s="4"/>
-      <c r="F198" s="5"/>
-      <c r="G198" s="5"/>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A199" s="4"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="D199" s="19" t="s">
+      <c r="E292" s="4"/>
+      <c r="F292" s="5"/>
+      <c r="G292" s="5"/>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A293" s="4"/>
+      <c r="B293" s="5"/>
+      <c r="C293" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="D293" s="19" t="s">
         <v>483</v>
       </c>
-      <c r="E199" s="4"/>
-      <c r="F199" s="5"/>
-      <c r="G199" s="5"/>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A200" s="4"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="D200" s="19" t="s">
+      <c r="E293" s="4"/>
+      <c r="F293" s="5"/>
+      <c r="G293" s="5"/>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A294" s="4"/>
+      <c r="B294" s="5"/>
+      <c r="C294" s="18" t="s">
+        <v>473</v>
+      </c>
+      <c r="D294" s="19" t="s">
         <v>484</v>
       </c>
-      <c r="E200" s="4"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="5"/>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A201" s="4"/>
-      <c r="B201" s="5"/>
-      <c r="C201" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="D201" s="19" t="s">
+      <c r="E294" s="4"/>
+      <c r="F294" s="5"/>
+      <c r="G294" s="5"/>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A295" s="4"/>
+      <c r="B295" s="5"/>
+      <c r="C295" s="18" t="s">
+        <v>474</v>
+      </c>
+      <c r="D295" s="19" t="s">
         <v>485</v>
       </c>
-      <c r="E201" s="4"/>
-      <c r="F201" s="5"/>
-      <c r="G201" s="5"/>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A202" s="4"/>
-      <c r="B202" s="5"/>
-      <c r="C202" s="18" t="s">
-        <v>474</v>
-      </c>
-      <c r="D202" s="19" t="s">
+      <c r="E295" s="4"/>
+      <c r="F295" s="5"/>
+      <c r="G295" s="5"/>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A296" s="4"/>
+      <c r="B296" s="5"/>
+      <c r="C296" s="18" t="s">
+        <v>475</v>
+      </c>
+      <c r="D296" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="E202" s="4"/>
-      <c r="F202" s="5"/>
-      <c r="G202" s="5"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A203" s="4"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="D203" s="19" t="s">
+      <c r="E296" s="4"/>
+      <c r="F296" s="5"/>
+      <c r="G296" s="5"/>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A297" s="4"/>
+      <c r="B297" s="5"/>
+      <c r="C297" s="18" t="s">
+        <v>476</v>
+      </c>
+      <c r="D297" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="E203" s="4"/>
-      <c r="F203" s="5"/>
-      <c r="G203" s="5"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A204" s="4"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="18" t="s">
-        <v>476</v>
-      </c>
-      <c r="D204" s="19" t="s">
+      <c r="E297" s="4"/>
+      <c r="F297" s="5"/>
+      <c r="G297" s="5"/>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A298" s="4"/>
+      <c r="B298" s="5"/>
+      <c r="C298" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="D298" s="19" t="s">
         <v>488</v>
       </c>
-      <c r="E204" s="4"/>
-      <c r="F204" s="5"/>
-      <c r="G204" s="5"/>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A205" s="4"/>
-      <c r="B205" s="5"/>
-      <c r="C205" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="D205" s="19" t="s">
+      <c r="E298" s="4"/>
+      <c r="F298" s="5"/>
+      <c r="G298" s="5"/>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A299" s="4"/>
+      <c r="B299" s="5"/>
+      <c r="C299" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="D299" s="19" t="s">
         <v>489</v>
       </c>
-      <c r="E205" s="4"/>
-      <c r="F205" s="5"/>
-      <c r="G205" s="5"/>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A206" s="4"/>
-      <c r="B206" s="5"/>
-      <c r="C206" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="D206" s="19" t="s">
+      <c r="E299" s="4"/>
+      <c r="F299" s="5"/>
+      <c r="G299" s="5"/>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A300" s="4"/>
+      <c r="B300" s="5"/>
+      <c r="C300" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="D300" s="19" t="s">
         <v>490</v>
       </c>
-      <c r="E206" s="4"/>
-      <c r="F206" s="5"/>
-      <c r="G206" s="5"/>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A207" s="4"/>
-      <c r="B207" s="5"/>
-      <c r="C207" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="D207" s="19" t="s">
+      <c r="E300" s="4"/>
+      <c r="F300" s="5"/>
+      <c r="G300" s="5"/>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A301" s="4"/>
+      <c r="B301" s="5"/>
+      <c r="C301" s="18" t="s">
+        <v>480</v>
+      </c>
+      <c r="D301" s="19" t="s">
         <v>492</v>
       </c>
-      <c r="E207" s="4"/>
-      <c r="F207" s="5"/>
-      <c r="G207" s="5"/>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A208" s="4"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="D208" s="19" t="s">
+      <c r="E301" s="4"/>
+      <c r="F301" s="5"/>
+      <c r="G301" s="5"/>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A302" s="4"/>
+      <c r="B302" s="5"/>
+      <c r="C302" s="18" t="s">
+        <v>481</v>
+      </c>
+      <c r="D302" s="19" t="s">
         <v>491</v>
       </c>
-      <c r="E208" s="4"/>
-      <c r="F208" s="5"/>
-      <c r="G208" s="5"/>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A209" s="4"/>
-      <c r="B209" s="5"/>
-      <c r="C209" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="D209" s="19" t="s">
+      <c r="E302" s="4"/>
+      <c r="F302" s="5"/>
+      <c r="G302" s="5"/>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A303" s="4"/>
+      <c r="B303" s="5"/>
+      <c r="C303" s="18" t="s">
+        <v>505</v>
+      </c>
+      <c r="D303" s="19" t="s">
         <v>493</v>
       </c>
-      <c r="E209" s="4"/>
-      <c r="F209" s="5"/>
-      <c r="G209" s="5"/>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A210" s="4"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="D210" s="19" t="s">
+      <c r="E303" s="4"/>
+      <c r="F303" s="5"/>
+      <c r="G303" s="5"/>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A304" s="4"/>
+      <c r="B304" s="5"/>
+      <c r="C304" s="18" t="s">
+        <v>506</v>
+      </c>
+      <c r="D304" s="19" t="s">
         <v>494</v>
       </c>
-      <c r="E210" s="4"/>
-      <c r="F210" s="5"/>
-      <c r="G210" s="5"/>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A211" s="4"/>
-      <c r="B211" s="5"/>
-      <c r="C211" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="D211" s="19" t="s">
+      <c r="E304" s="4"/>
+      <c r="F304" s="5"/>
+      <c r="G304" s="5"/>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A305" s="4"/>
+      <c r="B305" s="5"/>
+      <c r="C305" s="18" t="s">
+        <v>507</v>
+      </c>
+      <c r="D305" s="19" t="s">
         <v>495</v>
       </c>
-      <c r="E211" s="4"/>
-      <c r="F211" s="5"/>
-      <c r="G211" s="5"/>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A212" s="4"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="18" t="s">
-        <v>507</v>
-      </c>
-      <c r="D212" s="19" t="s">
+      <c r="E305" s="4"/>
+      <c r="F305" s="5"/>
+      <c r="G305" s="5"/>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A306" s="4"/>
+      <c r="B306" s="5"/>
+      <c r="C306" s="18" t="s">
+        <v>508</v>
+      </c>
+      <c r="D306" s="19" t="s">
         <v>496</v>
       </c>
-      <c r="E212" s="4"/>
-      <c r="F212" s="5"/>
-      <c r="G212" s="5"/>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A213" s="4"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="18" t="s">
-        <v>508</v>
-      </c>
-      <c r="D213" s="19" t="s">
+      <c r="E306" s="4"/>
+      <c r="F306" s="5"/>
+      <c r="G306" s="5"/>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A307" s="4"/>
+      <c r="B307" s="5"/>
+      <c r="C307" s="18" t="s">
+        <v>509</v>
+      </c>
+      <c r="D307" s="19" t="s">
         <v>497</v>
       </c>
-      <c r="E213" s="4"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="5"/>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A214" s="4"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="18" t="s">
-        <v>509</v>
-      </c>
-      <c r="D214" s="19" t="s">
+      <c r="E307" s="4"/>
+      <c r="F307" s="5"/>
+      <c r="G307" s="5"/>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A308" s="4"/>
+      <c r="B308" s="5"/>
+      <c r="C308" s="18" t="s">
+        <v>510</v>
+      </c>
+      <c r="D308" s="19" t="s">
         <v>498</v>
       </c>
-      <c r="E214" s="4"/>
-      <c r="F214" s="5"/>
-      <c r="G214" s="5"/>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A215" s="4"/>
-      <c r="B215" s="5"/>
-      <c r="C215" s="18" t="s">
-        <v>510</v>
-      </c>
-      <c r="D215" s="19" t="s">
+      <c r="E308" s="4"/>
+      <c r="F308" s="5"/>
+      <c r="G308" s="5"/>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A309" s="4"/>
+      <c r="B309" s="5"/>
+      <c r="C309" s="18" t="s">
+        <v>511</v>
+      </c>
+      <c r="D309" s="19" t="s">
         <v>499</v>
       </c>
-      <c r="E215" s="4"/>
-      <c r="F215" s="5"/>
-      <c r="G215" s="5"/>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A216" s="4"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="D216" s="19" t="s">
+      <c r="E309" s="4"/>
+      <c r="F309" s="5"/>
+      <c r="G309" s="5"/>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A310" s="4"/>
+      <c r="B310" s="5"/>
+      <c r="C310" s="18" t="s">
+        <v>512</v>
+      </c>
+      <c r="D310" s="19" t="s">
         <v>500</v>
       </c>
-      <c r="E216" s="4"/>
-      <c r="F216" s="5"/>
-      <c r="G216" s="5"/>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A217" s="4"/>
-      <c r="B217" s="5"/>
-      <c r="C217" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="D217" s="19" t="s">
+      <c r="E310" s="4"/>
+      <c r="F310" s="5"/>
+      <c r="G310" s="5"/>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A311" s="4"/>
+      <c r="B311" s="5"/>
+      <c r="C311" s="18" t="s">
+        <v>513</v>
+      </c>
+      <c r="D311" s="19" t="s">
         <v>501</v>
       </c>
-      <c r="E217" s="4"/>
-      <c r="F217" s="5"/>
-      <c r="G217" s="5"/>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A218" s="4"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="D218" s="19" t="s">
+      <c r="E311" s="4"/>
+      <c r="F311" s="5"/>
+      <c r="G311" s="5"/>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A312" s="4"/>
+      <c r="B312" s="5"/>
+      <c r="C312" s="18" t="s">
+        <v>514</v>
+      </c>
+      <c r="D312" s="19" t="s">
         <v>502</v>
       </c>
-      <c r="E218" s="4"/>
-      <c r="F218" s="5"/>
-      <c r="G218" s="5"/>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A219" s="4"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="D219" s="19" t="s">
+      <c r="E312" s="4"/>
+      <c r="F312" s="5"/>
+      <c r="G312" s="5"/>
+    </row>
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A313" s="4"/>
+      <c r="B313" s="5"/>
+      <c r="C313" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="D313" s="19" t="s">
         <v>503</v>
       </c>
-      <c r="E219" s="4"/>
-      <c r="F219" s="5"/>
-      <c r="G219" s="5"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A220" s="4"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="D220" s="19" t="s">
+      <c r="E313" s="4"/>
+      <c r="F313" s="5"/>
+      <c r="G313" s="5"/>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A314" s="4"/>
+      <c r="B314" s="5"/>
+      <c r="C314" s="18" t="s">
+        <v>516</v>
+      </c>
+      <c r="D314" s="19" t="s">
         <v>504</v>
       </c>
-      <c r="E220" s="4"/>
-      <c r="F220" s="5"/>
-      <c r="G220" s="5"/>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A221" s="4"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="D221" s="19" t="s">
+      <c r="E314" s="4"/>
+      <c r="F314" s="5"/>
+      <c r="G314" s="5"/>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D315" s="19" t="s">
         <v>517</v>
       </c>
-      <c r="E221" s="4"/>
-      <c r="F221" s="5"/>
-      <c r="G221" s="5"/>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A223" s="4"/>
-      <c r="B223" s="5" t="s">
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A316" s="4"/>
+      <c r="B316" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="C223" s="4" t="s">
+      <c r="C316" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="D223" s="19" t="s">
+      <c r="E316" s="4"/>
+      <c r="F316" s="5"/>
+      <c r="G316" s="5"/>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A317" s="4"/>
+      <c r="B317" s="5"/>
+      <c r="C317" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D317" s="19" t="s">
         <v>559</v>
       </c>
-      <c r="E223" s="4"/>
-      <c r="F223" s="5"/>
-      <c r="G223" s="5"/>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A224" s="4"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="D224" s="19" t="s">
+      <c r="E317" s="4"/>
+      <c r="F317" s="5"/>
+      <c r="G317" s="5"/>
+    </row>
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D318" s="19" t="s">
         <v>561</v>
       </c>
-      <c r="E224" s="4"/>
-      <c r="F224" s="5"/>
-      <c r="G224" s="5"/>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A226" s="4"/>
-      <c r="B226" s="5" t="s">
+    </row>
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A319" s="4"/>
+      <c r="B319" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="C226" s="4" t="s">
+      <c r="C319" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="D226" s="16" t="s">
+      <c r="E319" s="4"/>
+      <c r="F319" s="5"/>
+      <c r="G319" s="5"/>
+    </row>
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A320" s="4"/>
+      <c r="B320" s="5"/>
+      <c r="C320" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="D320" s="16" t="s">
         <v>562</v>
       </c>
-      <c r="E226" s="4"/>
-      <c r="F226" s="5"/>
-      <c r="G226" s="5"/>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A227" s="4"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="4" t="s">
+      <c r="E320" s="4"/>
+      <c r="F320" s="5"/>
+      <c r="G320" s="5"/>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A321" s="4"/>
+      <c r="B321" s="5"/>
+      <c r="C321" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="D321" s="16" t="s">
         <v>563</v>
       </c>
-      <c r="D227" s="16" t="s">
-        <v>563</v>
-      </c>
-      <c r="E227" s="4"/>
-      <c r="F227" s="5"/>
-      <c r="G227" s="5"/>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A228" s="4"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="4" t="s">
+      <c r="E321" s="4"/>
+      <c r="F321" s="5"/>
+      <c r="G321" s="5"/>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A322" s="4"/>
+      <c r="B322" s="5"/>
+      <c r="C322" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D322" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="D228" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="E228" s="4"/>
-      <c r="F228" s="5"/>
-      <c r="G228" s="5"/>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A229" s="4"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="4" t="s">
+      <c r="E322" s="4"/>
+      <c r="F322" s="5"/>
+      <c r="G322" s="5"/>
+    </row>
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A323" s="4"/>
+      <c r="B323" s="5"/>
+      <c r="C323" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="D323" s="16" t="s">
         <v>565</v>
       </c>
-      <c r="D229" s="16" t="s">
-        <v>565</v>
-      </c>
-      <c r="E229" s="4"/>
-      <c r="F229" s="5"/>
-      <c r="G229" s="5"/>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A230" s="4"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="4" t="s">
+      <c r="E323" s="4"/>
+      <c r="F323" s="5"/>
+      <c r="G323" s="5"/>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A324" s="4"/>
+      <c r="B324" s="5"/>
+      <c r="C324" s="4"/>
+      <c r="D324" s="16" t="s">
         <v>566</v>
       </c>
-      <c r="D230" s="16" t="s">
-        <v>566</v>
-      </c>
-      <c r="E230" s="4"/>
-      <c r="F230" s="5"/>
-      <c r="G230" s="5"/>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A231" s="4"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="4"/>
-      <c r="D231" s="5"/>
-      <c r="E231" s="4"/>
-      <c r="F231" s="5"/>
-      <c r="G231" s="5"/>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A232" s="4"/>
-      <c r="B232" s="5" t="s">
+      <c r="E324" s="4"/>
+      <c r="F324" s="5"/>
+      <c r="G324" s="5"/>
+    </row>
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A325" s="4"/>
+      <c r="B325" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="C232" s="4" t="s">
+      <c r="C325" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="D232" s="16" t="s">
+      <c r="D325" s="5"/>
+      <c r="E325" s="4"/>
+      <c r="F325" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G325" s="5"/>
+    </row>
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A326" s="4"/>
+      <c r="B326" s="5"/>
+      <c r="C326" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="D326" s="16" t="s">
         <v>583</v>
       </c>
-      <c r="E232" s="4"/>
-      <c r="F232" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="G232" s="5"/>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A233" s="4"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="D233" s="16" t="s">
+      <c r="E326" s="4"/>
+      <c r="F326" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="G326" s="5"/>
+    </row>
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A327" s="4"/>
+      <c r="B327" s="5"/>
+      <c r="C327" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="D327" s="16" t="s">
         <v>584</v>
       </c>
-      <c r="E233" s="4"/>
-      <c r="F233" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="G233" s="5"/>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A234" s="4"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="D234" s="16" t="s">
+      <c r="E327" s="4"/>
+      <c r="F327" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="G327" s="5"/>
+    </row>
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A328" s="4"/>
+      <c r="B328" s="5"/>
+      <c r="C328" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="D328" s="16" t="s">
         <v>585</v>
       </c>
-      <c r="E234" s="4"/>
-      <c r="F234" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="G234" s="5"/>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A235" s="4"/>
-      <c r="B235" s="5"/>
-      <c r="C235" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="D235" s="16" t="s">
+      <c r="E328" s="4"/>
+      <c r="F328" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="G328" s="5"/>
+    </row>
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A329" s="4"/>
+      <c r="B329" s="5"/>
+      <c r="C329" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D329" s="16" t="s">
         <v>587</v>
       </c>
-      <c r="E235" s="4"/>
-      <c r="F235" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="G235" s="5"/>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A236" s="4"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="4" t="s">
+      <c r="E329" s="4"/>
+      <c r="F329" s="5"/>
+      <c r="G329" s="5"/>
+    </row>
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A330" s="4"/>
+      <c r="B330" s="5"/>
+      <c r="C330" s="4"/>
+      <c r="D330" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="D236" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="E236" s="4"/>
-      <c r="F236" s="5"/>
-      <c r="G236" s="5"/>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A237" s="4"/>
-      <c r="B237" s="5"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="5"/>
-      <c r="E237" s="4"/>
-      <c r="F237" s="5"/>
-      <c r="G237" s="5"/>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A238" s="4"/>
-      <c r="B238" s="5" t="s">
+      <c r="E330" s="4"/>
+      <c r="F330" s="5"/>
+      <c r="G330" s="5"/>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A331" s="4"/>
+      <c r="B331" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="C238" s="4" t="s">
+      <c r="C331" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="D238" s="16" t="s">
+      <c r="D331" s="5"/>
+      <c r="E331" s="4"/>
+      <c r="F331" s="5"/>
+      <c r="G331" s="5"/>
+    </row>
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A332" s="4"/>
+      <c r="B332" s="5"/>
+      <c r="C332" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D332" s="16" t="s">
         <v>575</v>
       </c>
-      <c r="E238" s="4"/>
-      <c r="F238" s="5"/>
-      <c r="G238" s="5"/>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A239" s="4"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="4" t="s">
+      <c r="E332" s="4"/>
+      <c r="F332" s="5"/>
+      <c r="G332" s="5"/>
+    </row>
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A333" s="4"/>
+      <c r="B333" s="5"/>
+      <c r="C333" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D333" s="16" t="s">
         <v>576</v>
       </c>
-      <c r="D239" s="16" t="s">
-        <v>576</v>
-      </c>
-      <c r="E239" s="4"/>
-      <c r="F239" s="5"/>
-      <c r="G239" s="5"/>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A240" s="4"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="4" t="s">
+      <c r="E333" s="4"/>
+      <c r="F333" s="5"/>
+      <c r="G333" s="5"/>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A334" s="4"/>
+      <c r="B334" s="5"/>
+      <c r="C334" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="D334" s="16" t="s">
         <v>577</v>
       </c>
-      <c r="D240" s="16" t="s">
-        <v>577</v>
-      </c>
-      <c r="E240" s="4"/>
-      <c r="F240" s="5"/>
-      <c r="G240" s="5"/>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A241" s="4"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="4" t="s">
+      <c r="E334" s="4"/>
+      <c r="F334" s="5"/>
+      <c r="G334" s="5"/>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A335" s="4"/>
+      <c r="B335" s="5"/>
+      <c r="C335" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="D335" s="16" t="s">
         <v>578</v>
       </c>
-      <c r="D241" s="16" t="s">
-        <v>578</v>
-      </c>
-      <c r="E241" s="4"/>
-      <c r="F241" s="5"/>
-      <c r="G241" s="5"/>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A242" s="4"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="4" t="s">
+      <c r="E335" s="4"/>
+      <c r="F335" s="5"/>
+      <c r="G335" s="5"/>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D336" s="16" t="s">
         <v>579</v>
       </c>
-      <c r="D242" s="16" t="s">
-        <v>579</v>
-      </c>
-      <c r="E242" s="4"/>
-      <c r="F242" s="5"/>
-      <c r="G242" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/Images for Markdown files database updated 30-06-2026.xlsx
+++ b/Images for Markdown files database updated 30-06-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\trevor\Compac Industries\Compac - General\IT\ChatBot\Markdown-Manuals\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E14764-2D10-4280-BEF1-04F9F31624BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD687A7-09BE-4A9E-BB08-7D832916EFDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="-1320" windowWidth="38640" windowHeight="21120" xr2:uid="{7323B22B-375C-41F7-91CD-F86C900FC6DE}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1166" uniqueCount="701">
   <si>
     <t xml:space="preserve">PCBs </t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>K Factor switch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comms </t>
   </si>
   <si>
     <t>GPIO</t>
@@ -847,9 +844,6 @@
     <t>Various electronic</t>
   </si>
   <si>
-    <t xml:space="preserve">Mechanical </t>
-  </si>
-  <si>
     <t>10.1.1_Pump_Flange.png</t>
   </si>
   <si>
@@ -2081,6 +2075,78 @@
   </si>
   <si>
     <t>12.99.1_LITE_layout.png</t>
+  </si>
+  <si>
+    <t>Valve Modulation</t>
+  </si>
+  <si>
+    <t>13.1.1</t>
+  </si>
+  <si>
+    <t>13.1.2</t>
+  </si>
+  <si>
+    <t>13.1.3</t>
+  </si>
+  <si>
+    <t>13.1.4</t>
+  </si>
+  <si>
+    <t>13.2.1</t>
+  </si>
+  <si>
+    <t>13.2.2</t>
+  </si>
+  <si>
+    <t>13.1.1_modulation_pid.png</t>
+  </si>
+  <si>
+    <t>13.1.3_modulation_preset_graph.png</t>
+  </si>
+  <si>
+    <t>13.1.2_modulation_flow_graph.png</t>
+  </si>
+  <si>
+    <t>13.1.4_modulation_elec.schematic.png</t>
+  </si>
+  <si>
+    <t>13.2.1_modulation_PP1.png</t>
+  </si>
+  <si>
+    <t>13.2.2_modulation_PP2.png</t>
+  </si>
+  <si>
+    <t>13.2.3</t>
+  </si>
+  <si>
+    <t>13.2.4</t>
+  </si>
+  <si>
+    <t>13.2.5</t>
+  </si>
+  <si>
+    <t>13.2.3_modulation_PP3.png</t>
+  </si>
+  <si>
+    <t>13.2.4_modulation_PP4.png</t>
+  </si>
+  <si>
+    <t>13.2.5_modulation_PP5.png</t>
+  </si>
+  <si>
+    <t>Comfill</t>
+  </si>
+  <si>
+    <t>C5000</t>
+  </si>
+  <si>
+    <t>MR800S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI533 Comms connections </t>
+  </si>
+  <si>
+    <t>Mechanical  - Pumps</t>
   </si>
 </sst>
 </file>
@@ -2118,7 +2184,7 @@
       <name val="HelveticaNeue LT 57 Cn"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2149,8 +2215,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -2173,11 +2263,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2222,13 +2338,55 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2563,30 +2721,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B533B56-556A-40A2-8D3F-E8E5A852019A}">
-  <dimension ref="A1:G336"/>
+  <dimension ref="A1:K347"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.7265625" customWidth="1"/>
     <col min="3" max="3" width="10.6328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="47.26953125" customWidth="1"/>
-    <col min="5" max="5" width="16" style="1" customWidth="1"/>
-    <col min="6" max="6" width="29.81640625" customWidth="1"/>
-    <col min="7" max="7" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="11" width="11.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E1" s="2"/>
       <c r="F1" s="5"/>
@@ -2597,13 +2755,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="5"/>
@@ -2613,10 +2771,10 @@
       <c r="A3" s="4"/>
       <c r="B3" s="5"/>
       <c r="C3" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="5"/>
@@ -2626,10 +2784,10 @@
       <c r="A4" s="4"/>
       <c r="B4" s="5"/>
       <c r="C4" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E4" s="4"/>
       <c r="F4" s="5"/>
@@ -2639,10 +2797,10 @@
       <c r="A5" s="4"/>
       <c r="B5" s="5"/>
       <c r="C5" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
@@ -2665,10 +2823,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
@@ -2678,10 +2836,10 @@
       <c r="A8" s="4"/>
       <c r="B8" s="5"/>
       <c r="C8" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E8" s="4"/>
       <c r="F8" s="5"/>
@@ -2691,10 +2849,10 @@
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
       <c r="C9" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E9" s="4"/>
       <c r="F9" s="5"/>
@@ -2704,10 +2862,10 @@
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="5"/>
@@ -2717,10 +2875,10 @@
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="5"/>
@@ -2730,7 +2888,7 @@
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="4"/>
@@ -2754,10 +2912,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E14" s="4"/>
       <c r="F14" s="5"/>
@@ -2767,10 +2925,10 @@
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
@@ -2780,10 +2938,10 @@
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E16" s="4"/>
       <c r="F16" s="5"/>
@@ -2793,10 +2951,10 @@
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E17" s="4"/>
       <c r="F17" s="5"/>
@@ -2806,10 +2964,10 @@
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E18" s="4"/>
       <c r="F18" s="5"/>
@@ -2819,10 +2977,10 @@
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="5"/>
@@ -2832,10 +2990,10 @@
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
       <c r="C20" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="5"/>
@@ -2845,10 +3003,10 @@
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
       <c r="C21" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="5"/>
@@ -2858,10 +3016,10 @@
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="5"/>
@@ -2871,10 +3029,10 @@
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
       <c r="C23" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E23" s="4"/>
       <c r="F23" s="5"/>
@@ -2884,10 +3042,10 @@
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
       <c r="C24" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E24" s="4"/>
       <c r="F24" s="5"/>
@@ -2897,10 +3055,10 @@
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
       <c r="C25" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E25" s="4"/>
       <c r="F25" s="5"/>
@@ -2910,10 +3068,10 @@
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
       <c r="C26" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E26" s="4"/>
       <c r="F26" s="5"/>
@@ -2923,10 +3081,10 @@
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
       <c r="C27" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="5"/>
@@ -2958,10 +3116,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="5"/>
@@ -2971,10 +3129,10 @@
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
       <c r="C31" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31" s="4"/>
       <c r="F31" s="5"/>
@@ -2984,146 +3142,146 @@
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
       <c r="C32" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E32" s="4"/>
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E33" s="4"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
       <c r="C34" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E34" s="4"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
       <c r="C35" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D35" s="5" t="s">
         <v>98</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>99</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
       <c r="C36" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
       <c r="C37" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E37" s="4"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
       <c r="C38" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E38" s="4"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
       <c r="C39" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
       <c r="C40" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="5" t="s">
         <v>108</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>109</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
       <c r="C41" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>110</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>111</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
       <c r="C42" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>113</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
       <c r="C43" s="4"/>
@@ -3132,553 +3290,709 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A44" s="6"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="6"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A45" s="4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A44" s="26"/>
+      <c r="B44" s="25"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="25"/>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A45" s="28">
         <v>5</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="29" t="s">
+        <v>699</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="28"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A46" s="28"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="28"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A47" s="28"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="28"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A48" s="28"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>33</v>
+      </c>
+      <c r="E48" s="28"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="29"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>34</v>
+      </c>
+      <c r="E49" s="28"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="28"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="E50" s="28"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="29"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A51" s="28"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>36</v>
+      </c>
+      <c r="E51" s="28"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A52" s="28"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" s="28"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A53" s="28"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="E53" s="28"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A54" s="28"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" s="28"/>
+      <c r="F54" s="29"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="29"/>
+      <c r="K54" s="29"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A55" s="28"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="29" t="s">
+        <v>41</v>
+      </c>
+      <c r="E55" s="28"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A56" s="28"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56" s="28"/>
+      <c r="F56" s="29"/>
+      <c r="G56" s="29"/>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29"/>
+      <c r="J56" s="29"/>
+      <c r="K56" s="29"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A57" s="28"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>42</v>
+      </c>
+      <c r="E57" s="28"/>
+      <c r="F57" s="29"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29"/>
+      <c r="J57" s="29"/>
+      <c r="K57" s="29"/>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A58" s="28"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="29" t="s">
+        <v>43</v>
+      </c>
+      <c r="E58" s="28"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A59" s="28"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E59" s="28"/>
+      <c r="F59" s="29"/>
+      <c r="G59" s="29"/>
+      <c r="H59" s="29"/>
+      <c r="I59" s="29"/>
+      <c r="J59" s="29"/>
+      <c r="K59" s="29"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A60" s="28"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>45</v>
+      </c>
+      <c r="E60" s="28"/>
+      <c r="F60" s="29"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="29"/>
+      <c r="I60" s="29"/>
+      <c r="J60" s="29"/>
+      <c r="K60" s="29"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A61" s="28"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E61" s="28"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A62" s="28"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="28"/>
+      <c r="F62" s="29"/>
+      <c r="G62" s="29"/>
+      <c r="H62" s="29"/>
+      <c r="I62" s="29"/>
+      <c r="J62" s="29"/>
+      <c r="K62" s="29"/>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A63" s="28"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" s="28"/>
+      <c r="F63" s="29"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="29"/>
+      <c r="K63" s="29"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A64" s="28"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E64" s="28"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A65" s="28"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="E65" s="28"/>
+      <c r="F65" s="29"/>
+      <c r="G65" s="29"/>
+      <c r="H65" s="29"/>
+      <c r="I65" s="29"/>
+      <c r="J65" s="29"/>
+      <c r="K65" s="29"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A66" s="28"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="29" t="s">
+        <v>51</v>
+      </c>
+      <c r="E66" s="28"/>
+      <c r="F66" s="29"/>
+      <c r="G66" s="29"/>
+      <c r="H66" s="29"/>
+      <c r="I66" s="29"/>
+      <c r="J66" s="29"/>
+      <c r="K66" s="29"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A67" s="28"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E67" s="28"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A68" s="26"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="26"/>
+      <c r="F68" s="25"/>
+      <c r="G68" s="25"/>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25"/>
+      <c r="J68" s="25"/>
+      <c r="K68" s="25"/>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A69" s="13">
+        <v>6</v>
+      </c>
+      <c r="B69" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E45" s="4"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E46" s="4"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A47" s="4"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E47" s="4"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E48" s="4"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A49" s="4"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E49" s="4"/>
-      <c r="F49" s="5"/>
-      <c r="G49" s="5"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E50" s="4"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A51" s="4"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E51" s="4"/>
-      <c r="F51" s="5"/>
-      <c r="G51" s="5"/>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A52" s="4"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="E52" s="4"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A53" s="4"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E53" s="4"/>
-      <c r="F53" s="5"/>
-      <c r="G53" s="5"/>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A54" s="4"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E54" s="4"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A55" s="4"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="E55" s="4"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A56" s="4"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A57" s="4"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="E57" s="4"/>
-      <c r="F57" s="5"/>
-      <c r="G57" s="5"/>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A58" s="4"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D58" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E58" s="4"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A59" s="4"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E59" s="4"/>
-      <c r="F59" s="5"/>
-      <c r="G59" s="5"/>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A60" s="4"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E60" s="4"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A61" s="4"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="5"/>
-      <c r="G61" s="5"/>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A62" s="4"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D62" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62" s="4"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A63" s="4"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E63" s="4"/>
-      <c r="F63" s="5"/>
-      <c r="G63" s="5"/>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A64" s="4"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E64" s="4"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A65" s="4"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A66" s="4"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D66" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E66" s="4"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A67" s="4"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D67" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="5"/>
-      <c r="G67" s="5"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A68" s="6"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="7"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A69" s="4">
-        <v>6</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>4</v>
-      </c>
       <c r="C69" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="D69" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D69" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="E69" s="4"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="5"/>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A70" s="4"/>
-      <c r="B70" s="5"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A70" s="13"/>
+      <c r="B70" s="12"/>
       <c r="C70" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D70" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D70" s="12" t="s">
+      <c r="E70" s="13"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
+      <c r="H70" s="12"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="13"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="E70" s="4"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A71" s="4"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="13" t="s">
+      <c r="D71" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="12"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="13"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D72" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E71" s="4"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A72" s="4"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="13" t="s">
+      <c r="E72" s="13"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="12"/>
+      <c r="H72" s="12"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A73" s="13"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D72" s="12" t="s">
+      <c r="D73" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="E72" s="4"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A73" s="4"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D73" s="12" t="s">
+      <c r="E73" s="13"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
+      <c r="H73" s="12"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A74" s="13"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D74" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="E73" s="4"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" s="4"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="13" t="s">
+      <c r="E74" s="13"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A75" s="13"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D75" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E74" s="4"/>
-      <c r="F74" s="5"/>
-      <c r="G74" s="5"/>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A75" s="4"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="13" t="s">
+      <c r="E75" s="13"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
+      <c r="K75" s="12"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A76" s="13"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="E76" s="13"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A77" s="13"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D77" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="D75" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E75" s="4"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A76" s="4"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="D76" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="5"/>
-      <c r="G76" s="5"/>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A77" s="4"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E77" s="4"/>
-      <c r="F77" s="5"/>
-      <c r="G77" s="5"/>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A78" s="4"/>
-      <c r="B78" s="5"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="12"/>
+      <c r="H77" s="12"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A78" s="13"/>
+      <c r="B78" s="12"/>
       <c r="C78" s="13" t="s">
+        <v>586</v>
+      </c>
+      <c r="D78" s="19" t="s">
+        <v>590</v>
+      </c>
+      <c r="E78" s="13"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="12"/>
+      <c r="H78" s="12"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A79" s="13"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="13" t="s">
+        <v>587</v>
+      </c>
+      <c r="D79" s="19" t="s">
+        <v>591</v>
+      </c>
+      <c r="E79" s="13"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A80" s="13"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="13" t="s">
         <v>588</v>
       </c>
-      <c r="D78" s="20" t="s">
+      <c r="D80" s="19" t="s">
         <v>592</v>
       </c>
-      <c r="E78" s="4"/>
-      <c r="F78" s="5"/>
-      <c r="G78" s="5"/>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A79" s="4"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="13" t="s">
+      <c r="E80" s="13"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="12"/>
+      <c r="H80" s="12"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="12"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A81" s="13"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="13" t="s">
         <v>589</v>
       </c>
-      <c r="D79" s="20" t="s">
+      <c r="D81" s="19" t="s">
         <v>593</v>
       </c>
-      <c r="E79" s="4"/>
-      <c r="F79" s="5"/>
-      <c r="G79" s="5"/>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A80" s="4"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="13" t="s">
-        <v>590</v>
-      </c>
-      <c r="D80" s="20" t="s">
-        <v>594</v>
-      </c>
-      <c r="E80" s="4"/>
-      <c r="F80" s="5"/>
-      <c r="G80" s="5"/>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A81" s="4"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="13" t="s">
-        <v>591</v>
-      </c>
-      <c r="D81" s="20" t="s">
-        <v>595</v>
-      </c>
-      <c r="E81" s="4"/>
-      <c r="F81" s="5"/>
-      <c r="G81" s="5"/>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A82" s="6"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="6"/>
-      <c r="D82" s="7"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="5"/>
-      <c r="G82" s="5"/>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E81" s="13"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="12"/>
+      <c r="H81" s="12"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A82" s="26"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="25"/>
+      <c r="G82" s="25"/>
+      <c r="H82" s="25"/>
+      <c r="I82" s="25"/>
+      <c r="J82" s="25"/>
+      <c r="K82" s="25"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>7</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E83" s="4"/>
       <c r="F83" s="5"/>
       <c r="G83" s="5"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="4"/>
       <c r="B84" s="5"/>
       <c r="C84" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E84" s="4"/>
       <c r="F84" s="5"/>
       <c r="G84" s="5"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="4"/>
       <c r="B85" s="5"/>
       <c r="C85" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E85" s="4"/>
       <c r="F85" s="5"/>
       <c r="G85" s="5"/>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="6"/>
       <c r="B86" s="7"/>
       <c r="C86" s="6"/>
@@ -3687,76 +4001,76 @@
       <c r="F86" s="5"/>
       <c r="G86" s="5"/>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>8</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E87" s="4"/>
       <c r="F87" s="5"/>
       <c r="G87" s="5"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="4"/>
       <c r="B88" s="5"/>
       <c r="C88" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E88" s="4"/>
       <c r="F88" s="5"/>
       <c r="G88" s="5"/>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="4"/>
       <c r="B89" s="5"/>
       <c r="C89" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E89" s="4"/>
       <c r="F89" s="5"/>
       <c r="G89" s="5"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="4"/>
       <c r="B90" s="5"/>
       <c r="C90" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E90" s="4"/>
       <c r="F90" s="5"/>
       <c r="G90" s="5"/>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="4"/>
       <c r="B91" s="5"/>
       <c r="C91" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E91" s="4"/>
       <c r="F91" s="5"/>
       <c r="G91" s="5"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="6"/>
       <c r="B92" s="7"/>
       <c r="C92" s="6"/>
@@ -3765,31 +4079,31 @@
       <c r="F92" s="5"/>
       <c r="G92" s="5"/>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>9</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C93" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D93" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="D93" s="5" t="s">
-        <v>150</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="5"/>
       <c r="G93" s="5"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="4"/>
       <c r="B94" s="5"/>
       <c r="C94" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D94" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="E94" s="17">
         <v>46098</v>
@@ -3797,98 +4111,98 @@
       <c r="F94" s="5"/>
       <c r="G94" s="5"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="4"/>
       <c r="B95" s="5"/>
       <c r="C95" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E95" s="4"/>
       <c r="F95" s="5"/>
       <c r="G95" s="5"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="4"/>
       <c r="B96" s="5"/>
       <c r="C96" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E96" s="4"/>
       <c r="F96" s="5"/>
       <c r="G96" s="5"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="4"/>
       <c r="B97" s="5"/>
       <c r="C97" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E97" s="4"/>
       <c r="F97" s="5"/>
       <c r="G97" s="5"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="4"/>
       <c r="B98" s="5"/>
       <c r="C98" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E98" s="4"/>
       <c r="F98" s="5"/>
       <c r="G98" s="5"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="4"/>
       <c r="B99" s="5"/>
       <c r="C99" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D99" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="E99" s="4"/>
       <c r="F99" s="5"/>
       <c r="G99" s="5"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="4"/>
       <c r="B100" s="5"/>
       <c r="C100" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D100" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D100" s="5" t="s">
-        <v>177</v>
       </c>
       <c r="E100" s="4"/>
       <c r="F100" s="5"/>
       <c r="G100" s="5"/>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="4"/>
       <c r="B101" s="5"/>
       <c r="C101" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D101" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="D101" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="E101" s="4"/>
       <c r="F101" s="5"/>
       <c r="G101" s="5"/>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="4"/>
       <c r="B102" s="5"/>
       <c r="C102" s="4"/>
@@ -3897,7 +4211,7 @@
       <c r="F102" s="5"/>
       <c r="G102" s="5"/>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="4"/>
       <c r="B103" s="5"/>
       <c r="C103" s="4"/>
@@ -3906,1381 +4220,1409 @@
       <c r="F103" s="5"/>
       <c r="G103" s="5"/>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A104" s="4"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A105" s="6"/>
-      <c r="B105" s="7"/>
-      <c r="C105" s="6"/>
-      <c r="D105" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E105" s="6"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A106" s="4"/>
-      <c r="B106" s="5" t="s">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A104" s="30"/>
+      <c r="B104" s="31"/>
+      <c r="C104" s="30"/>
+      <c r="D104" s="31"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="31"/>
+      <c r="G104" s="31"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A105" s="26"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E105" s="26"/>
+      <c r="F105" s="25"/>
+      <c r="G105" s="25"/>
+      <c r="H105" s="25"/>
+      <c r="I105" s="25"/>
+      <c r="J105" s="25"/>
+      <c r="K105" s="25"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106" s="35"/>
+      <c r="B106" s="36" t="s">
+        <v>700</v>
+      </c>
+      <c r="C106" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="D106" s="36" t="s">
+        <v>266</v>
+      </c>
+      <c r="E106" s="37">
+        <v>46098</v>
+      </c>
+      <c r="F106" s="36"/>
+      <c r="G106" s="36"/>
+      <c r="H106" s="36"/>
+      <c r="I106" s="36"/>
+      <c r="J106" s="36"/>
+      <c r="K106" s="36"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A107" s="35"/>
+      <c r="B107" s="36"/>
+      <c r="C107" s="35" t="s">
+        <v>181</v>
+      </c>
+      <c r="D107" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="D106" s="5" t="s">
+      <c r="E107" s="37">
+        <v>46098</v>
+      </c>
+      <c r="F107" s="36"/>
+      <c r="G107" s="36"/>
+      <c r="H107" s="36"/>
+      <c r="I107" s="36"/>
+      <c r="J107" s="36"/>
+      <c r="K107" s="36"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A108" s="35"/>
+      <c r="B108" s="36"/>
+      <c r="C108" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D108" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="E106" s="17">
+      <c r="E108" s="37">
         <v>46098</v>
       </c>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A107" s="4"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="4" t="s">
-        <v>182</v>
-      </c>
-      <c r="D107" s="5" t="s">
+      <c r="F108" s="36"/>
+      <c r="G108" s="36"/>
+      <c r="H108" s="36"/>
+      <c r="I108" s="36"/>
+      <c r="J108" s="36"/>
+      <c r="K108" s="36"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A109" s="35"/>
+      <c r="B109" s="36"/>
+      <c r="C109" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="D109" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="E107" s="17">
+      <c r="E109" s="37">
         <v>46098</v>
       </c>
-      <c r="F107" s="5"/>
-      <c r="G107" s="5"/>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A108" s="4"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D108" s="5" t="s">
+      <c r="F109" s="36"/>
+      <c r="G109" s="36"/>
+      <c r="H109" s="36"/>
+      <c r="I109" s="36"/>
+      <c r="J109" s="36"/>
+      <c r="K109" s="36"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A110" s="35"/>
+      <c r="B110" s="36"/>
+      <c r="C110" s="35"/>
+      <c r="D110" s="36"/>
+      <c r="E110" s="35"/>
+      <c r="F110" s="36"/>
+      <c r="G110" s="36"/>
+      <c r="H110" s="36"/>
+      <c r="I110" s="36"/>
+      <c r="J110" s="36"/>
+      <c r="K110" s="36"/>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A111" s="26"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="E111" s="26"/>
+      <c r="F111" s="25"/>
+      <c r="G111" s="25"/>
+      <c r="H111" s="25"/>
+      <c r="I111" s="25"/>
+      <c r="J111" s="25"/>
+      <c r="K111" s="25"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A112" s="32"/>
+      <c r="B112" s="33" t="s">
         <v>270</v>
       </c>
-      <c r="E108" s="17">
-        <v>46098</v>
-      </c>
-      <c r="F108" s="5"/>
-      <c r="G108" s="5"/>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A109" s="4"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D109" s="5" t="s">
+      <c r="C112" s="32" t="s">
         <v>271</v>
       </c>
-      <c r="E109" s="17">
-        <v>46098</v>
-      </c>
-      <c r="F109" s="5"/>
-      <c r="G109" s="5"/>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A110" s="4"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="4"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="4"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A111" s="6"/>
-      <c r="B111" s="7"/>
-      <c r="C111" s="6"/>
-      <c r="D111" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="E111" s="6"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A112" s="4"/>
-      <c r="B112" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="C112" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="E112" s="17">
+      <c r="D112" s="33" t="s">
+        <v>281</v>
+      </c>
+      <c r="E112" s="34">
         <v>46099</v>
       </c>
-      <c r="F112" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="G112" s="5" t="s">
-        <v>327</v>
+      <c r="F112" s="33" t="s">
+        <v>329</v>
+      </c>
+      <c r="G112" s="33" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="4"/>
       <c r="B113" s="5"/>
       <c r="C113" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E113" s="17">
         <v>46099</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G113" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="4"/>
       <c r="B114" s="5"/>
       <c r="C114" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E114" s="17">
         <v>46099</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G114" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="4"/>
       <c r="B115" s="5"/>
       <c r="C115" s="4" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E115" s="17">
         <v>46099</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G115" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="4"/>
       <c r="B116" s="5"/>
       <c r="C116" s="4" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E116" s="17">
         <v>46099</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G116" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="4"/>
       <c r="B117" s="5"/>
       <c r="C117" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E117" s="17">
         <v>46099</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G117" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="4"/>
       <c r="B118" s="5"/>
       <c r="C118" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E118" s="17">
         <v>46099</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="4"/>
       <c r="B119" s="5"/>
       <c r="C119" s="4" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E119" s="17">
         <v>46099</v>
       </c>
       <c r="F119" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>325</v>
-      </c>
-      <c r="G119" s="5" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="4"/>
       <c r="B120" s="5"/>
       <c r="C120" s="4" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E120" s="17">
         <v>46099</v>
       </c>
       <c r="F120" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="G120" s="5" t="s">
         <v>325</v>
-      </c>
-      <c r="G120" s="5" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="4"/>
       <c r="B121" s="5"/>
       <c r="C121" s="4" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E121" s="17">
         <v>46099</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G121" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="4"/>
       <c r="B122" s="5"/>
       <c r="C122" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E122" s="17">
         <v>46099</v>
       </c>
       <c r="F122" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G122" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="4"/>
       <c r="B123" s="5"/>
       <c r="C123" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D123" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="D123" s="5" t="s">
-        <v>297</v>
       </c>
       <c r="E123" s="17">
         <v>46099</v>
       </c>
       <c r="F123" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G123" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="4"/>
       <c r="B124" s="5"/>
       <c r="C124" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E124" s="17">
         <v>46099</v>
       </c>
       <c r="F124" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G124" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="4"/>
       <c r="B125" s="5"/>
       <c r="C125" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E125" s="17">
         <v>46099</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G125" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="4"/>
       <c r="B126" s="5"/>
       <c r="C126" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E126" s="17">
         <v>46099</v>
       </c>
       <c r="F126" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G126" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="4"/>
       <c r="B127" s="5"/>
       <c r="C127" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E127" s="17">
         <v>46099</v>
       </c>
       <c r="F127" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G127" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="4"/>
       <c r="B128" s="5"/>
       <c r="C128" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E128" s="17">
         <v>46099</v>
       </c>
       <c r="F128" s="5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="G128" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="4"/>
       <c r="B129" s="5"/>
       <c r="C129" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E129" s="17">
         <v>46099</v>
       </c>
       <c r="F129" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G129" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="4"/>
       <c r="B130" s="5"/>
       <c r="C130" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E130" s="17">
         <v>46099</v>
       </c>
       <c r="F130" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G130" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="4"/>
       <c r="B131" s="5"/>
       <c r="C131" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E131" s="17">
         <v>46099</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G131" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="4"/>
       <c r="B132" s="5"/>
       <c r="C132" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E132" s="17">
         <v>46099</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G132" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="4"/>
       <c r="B133" s="5"/>
       <c r="C133" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E133" s="17">
         <v>46099</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G133" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="4"/>
       <c r="B134" s="5"/>
       <c r="C134" s="4" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E134" s="17">
         <v>46099</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G134" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="4"/>
       <c r="B135" s="5"/>
       <c r="C135" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E135" s="17">
         <v>46099</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="4"/>
       <c r="B136" s="5"/>
       <c r="C136" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E136" s="17">
         <v>46099</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G136" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="4"/>
       <c r="B137" s="5"/>
       <c r="C137" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E137" s="17">
         <v>46099</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G137" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="4"/>
       <c r="B138" s="5"/>
       <c r="C138" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E138" s="17">
         <v>46099</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G138" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="4"/>
       <c r="B139" s="5"/>
       <c r="C139" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E139" s="17">
         <v>46099</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G139" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="4"/>
       <c r="B140" s="5"/>
       <c r="C140" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E140" s="17">
         <v>46099</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G140" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="4"/>
       <c r="B141" s="5"/>
       <c r="C141" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E141" s="17">
         <v>46099</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G141" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="4"/>
       <c r="B142" s="5"/>
       <c r="C142" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E142" s="17">
         <v>46099</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G142" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="4"/>
       <c r="B143" s="5"/>
       <c r="C143" s="4" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E143" s="17">
         <v>46099</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G143" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="4"/>
       <c r="B144" s="5"/>
       <c r="C144" s="4" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E144" s="17">
         <v>46099</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G144" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="4"/>
       <c r="B145" s="5"/>
       <c r="C145" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E145" s="17">
         <v>46099</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G145" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="4"/>
       <c r="B146" s="5"/>
       <c r="C146" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E146" s="17">
         <v>46099</v>
       </c>
       <c r="F146" s="5" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G146" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="4"/>
       <c r="B147" s="5"/>
       <c r="C147" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E147" s="17">
         <v>46099</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G147" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="4"/>
       <c r="B148" s="5"/>
       <c r="C148" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E148" s="17">
         <v>46099</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G148" s="5" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="4"/>
       <c r="B149" s="5"/>
       <c r="C149" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E149" s="17">
         <v>46099</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="4"/>
       <c r="B150" s="5"/>
       <c r="C150" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E150" s="17">
         <v>46099</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G150" s="5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="4"/>
       <c r="B151" s="5"/>
       <c r="C151" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E151" s="17">
         <v>46099</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G151" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="4"/>
       <c r="B152" s="5"/>
       <c r="C152" s="4" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E152" s="17">
         <v>46099</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G152" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="4"/>
       <c r="B153" s="5"/>
       <c r="C153" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E153" s="17">
         <v>46099</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="G153" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="4"/>
       <c r="B154" s="5"/>
       <c r="C154" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E154" s="17">
         <v>46099</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G154" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="4"/>
       <c r="B155" s="5"/>
       <c r="C155" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E155" s="17">
         <v>46099</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="4"/>
       <c r="B156" s="5"/>
       <c r="C156" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E156" s="17">
         <v>46099</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="G156" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="4"/>
       <c r="B157" s="5"/>
       <c r="C157" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E157" s="17">
         <v>46099</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="G157" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="4"/>
       <c r="B158" s="5"/>
       <c r="C158" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E158" s="17">
         <v>46099</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="G158" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="4"/>
       <c r="B159" s="5"/>
       <c r="C159" s="4" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E159" s="17">
         <v>46099</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="G159" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="4"/>
       <c r="B160" s="5"/>
       <c r="C160" s="4" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E160" s="17">
         <v>46099</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G160" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="4"/>
       <c r="B161" s="5"/>
       <c r="C161" s="4" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E161" s="17">
         <v>46099</v>
       </c>
       <c r="F161" s="5" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="G161" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="4"/>
       <c r="B162" s="5"/>
       <c r="C162" s="4" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E162" s="17">
         <v>46099</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G162" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="4"/>
       <c r="B163" s="5"/>
       <c r="C163" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E163" s="17">
         <v>46099</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G163" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="4"/>
       <c r="B164" s="5"/>
       <c r="C164" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E164" s="17">
         <v>46099</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="G164" s="5" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="4"/>
       <c r="B165" s="5"/>
       <c r="C165" s="4" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E165" s="17">
         <v>46099</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G165" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="4"/>
       <c r="B166" s="5"/>
       <c r="C166" s="4" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E166" s="17">
         <v>46099</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G166" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="4"/>
       <c r="B167" s="5"/>
       <c r="C167" s="4" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E167" s="17">
         <v>46099</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G167" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="4"/>
       <c r="B168" s="5"/>
       <c r="C168" s="4" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E168" s="17">
         <v>46099</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G168" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="4"/>
       <c r="B169" s="5"/>
       <c r="C169" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E169" s="17">
         <v>46099</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G169" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="4"/>
       <c r="B170" s="5"/>
       <c r="C170" s="4" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E170" s="17">
         <v>46099</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G170" s="5" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="4"/>
       <c r="B171" s="5"/>
       <c r="C171" s="4" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E171" s="17">
         <v>46099</v>
       </c>
       <c r="F171" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G171" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="4"/>
       <c r="B172" s="5"/>
       <c r="C172" s="4" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E172" s="17">
         <v>46099</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G172" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="4"/>
       <c r="B173" s="5"/>
       <c r="C173" s="4" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E173" s="17">
         <v>46099</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="4"/>
       <c r="B174" s="5"/>
       <c r="C174" s="4" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E174" s="17">
         <v>46099</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="4"/>
       <c r="B175" s="5"/>
       <c r="C175" s="4" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E175" s="17">
         <v>46099</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="4"/>
       <c r="B176" s="5"/>
       <c r="C176" s="4" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E176" s="17">
         <v>46099</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G176" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="4"/>
       <c r="B177" s="5"/>
       <c r="C177" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E177" s="17">
         <v>46099</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="G177" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="4"/>
       <c r="B178" s="5"/>
       <c r="C178" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E178" s="17">
         <v>46099</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G178" s="5" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.35">
@@ -5294,1141 +5636,1465 @@
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C181" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C182" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C183" s="1" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C184" s="1" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C185" s="1" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C186" s="1" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C187" s="1" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C188" s="1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C189" s="1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C190" s="1" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C191" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C192" s="1" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="193" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C193" s="1" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="194" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C194" s="1" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="195" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C195" s="1" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="196" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C196" s="1" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="197" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C197" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="198" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C198" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="199" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C199" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="200" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C200" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="201" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C201" s="1" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="202" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C202" s="1" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="203" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C203" s="1" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
     </row>
     <row r="204" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C204" s="1" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="205" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C205" s="1" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="206" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C206" s="1" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="207" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C207" s="1" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="208" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C208" s="1" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="209" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C209" s="1" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="210" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C210" s="1" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="211" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C211" s="1" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="212" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C212" s="1" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="213" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C213" s="1" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="214" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C214" s="1" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="215" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C215" s="1" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="216" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C216" s="1" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="217" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C217" s="1" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="218" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C218" s="1" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
     </row>
     <row r="219" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C219" s="1" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="220" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C220" s="1" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="221" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C221" s="1" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="222" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C222" s="1" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
     </row>
     <row r="223" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C223" s="1" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="224" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C224" s="1" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
     </row>
     <row r="225" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C225" s="1" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="226" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C226" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
     </row>
     <row r="227" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C227" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="228" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C228" s="1" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="229" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C229" s="1" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="230" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C230" s="1" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="231" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C231" s="1" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="232" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C232" s="1" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
     </row>
     <row r="233" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C233" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="234" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C234" s="1" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
     </row>
     <row r="235" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C235" s="1" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="236" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C236" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
     </row>
     <row r="237" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C237" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="238" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C238" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
     </row>
     <row r="239" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C239" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="240" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C240" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="241" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C241" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="242" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C242" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="243" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C243" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="244" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C244" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="245" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C245" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="246" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C246" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="247" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C247" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="248" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C248" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="249" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C249" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="250" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C250" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="251" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C251" s="1" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="252" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C252" s="1" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="253" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C253" s="1" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="254" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C254" s="1" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="255" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C255" s="1" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="256" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C256" s="1" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C257" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C258" s="1" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="257" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C257" s="1" t="s">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B260" t="s">
         <v>672</v>
       </c>
-    </row>
-    <row r="258" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C258" s="1" t="s">
+      <c r="C260" s="1" t="s">
         <v>673</v>
       </c>
-    </row>
-    <row r="260" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B260" t="s">
+      <c r="D260" t="s">
         <v>674</v>
       </c>
-      <c r="C260" s="1" t="s">
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C261" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="D260" t="s">
+      <c r="D261" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="261" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C261" s="1" t="s">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A262" s="20"/>
+      <c r="B262" s="21"/>
+      <c r="C262" s="20"/>
+      <c r="D262" s="21"/>
+      <c r="E262" s="20"/>
+      <c r="F262" s="21"/>
+      <c r="G262" s="21"/>
+      <c r="H262" s="21"/>
+      <c r="I262" s="21"/>
+      <c r="J262" s="21"/>
+      <c r="K262" s="21"/>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A263" s="22">
+        <v>13</v>
+      </c>
+      <c r="B263" s="23" t="s">
         <v>677</v>
       </c>
-      <c r="D261" t="s">
+      <c r="C263" s="22" t="s">
         <v>678</v>
       </c>
-    </row>
-    <row r="270" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C270" s="1" t="s">
+      <c r="D263" s="24" t="s">
+        <v>684</v>
+      </c>
+      <c r="E263" s="22" t="s">
+        <v>696</v>
+      </c>
+      <c r="F263" s="22" t="s">
+        <v>697</v>
+      </c>
+      <c r="G263" s="24" t="s">
+        <v>698</v>
+      </c>
+      <c r="H263" s="24"/>
+      <c r="I263" s="24"/>
+      <c r="J263" s="24"/>
+      <c r="K263" s="24"/>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A264" s="22"/>
+      <c r="B264" s="24"/>
+      <c r="C264" s="22" t="s">
+        <v>679</v>
+      </c>
+      <c r="D264" s="24" t="s">
+        <v>686</v>
+      </c>
+      <c r="E264" s="22"/>
+      <c r="F264" s="24"/>
+      <c r="G264" s="24"/>
+      <c r="H264" s="24"/>
+      <c r="I264" s="24"/>
+      <c r="J264" s="24"/>
+      <c r="K264" s="24"/>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A265" s="22"/>
+      <c r="B265" s="24"/>
+      <c r="C265" s="22" t="s">
+        <v>680</v>
+      </c>
+      <c r="D265" s="24" t="s">
+        <v>685</v>
+      </c>
+      <c r="E265" s="22"/>
+      <c r="F265" s="24"/>
+      <c r="G265" s="24"/>
+      <c r="H265" s="24"/>
+      <c r="I265" s="24"/>
+      <c r="J265" s="24"/>
+      <c r="K265" s="24"/>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A266" s="22"/>
+      <c r="B266" s="24"/>
+      <c r="C266" s="22" t="s">
+        <v>681</v>
+      </c>
+      <c r="D266" s="24" t="s">
+        <v>687</v>
+      </c>
+      <c r="E266" s="22"/>
+      <c r="F266" s="24"/>
+      <c r="G266" s="24"/>
+      <c r="H266" s="24"/>
+      <c r="I266" s="24"/>
+      <c r="J266" s="24"/>
+      <c r="K266" s="24"/>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A267" s="22"/>
+      <c r="B267" s="24"/>
+      <c r="C267" s="22" t="s">
+        <v>682</v>
+      </c>
+      <c r="D267" s="24" t="s">
+        <v>688</v>
+      </c>
+      <c r="E267" s="22"/>
+      <c r="F267" s="24"/>
+      <c r="G267" s="24"/>
+      <c r="H267" s="24"/>
+      <c r="I267" s="24"/>
+      <c r="J267" s="24"/>
+      <c r="K267" s="24"/>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A268" s="22"/>
+      <c r="B268" s="24"/>
+      <c r="C268" s="22" t="s">
+        <v>683</v>
+      </c>
+      <c r="D268" s="24" t="s">
+        <v>689</v>
+      </c>
+      <c r="E268" s="22"/>
+      <c r="F268" s="24"/>
+      <c r="G268" s="24"/>
+      <c r="H268" s="24"/>
+      <c r="I268" s="24"/>
+      <c r="J268" s="24"/>
+      <c r="K268" s="24"/>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A269" s="22"/>
+      <c r="B269" s="24"/>
+      <c r="C269" s="22" t="s">
+        <v>690</v>
+      </c>
+      <c r="D269" s="24" t="s">
+        <v>693</v>
+      </c>
+      <c r="E269" s="22"/>
+      <c r="F269" s="24"/>
+      <c r="G269" s="24"/>
+      <c r="H269" s="24"/>
+      <c r="I269" s="24"/>
+      <c r="J269" s="24"/>
+      <c r="K269" s="24"/>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A270" s="22"/>
+      <c r="B270" s="24"/>
+      <c r="C270" s="22" t="s">
+        <v>691</v>
+      </c>
+      <c r="D270" s="24" t="s">
+        <v>694</v>
+      </c>
+      <c r="E270" s="22"/>
+      <c r="F270" s="24"/>
+      <c r="G270" s="24"/>
+      <c r="H270" s="24"/>
+      <c r="I270" s="24"/>
+      <c r="J270" s="24"/>
+      <c r="K270" s="24"/>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A271" s="22"/>
+      <c r="B271" s="24"/>
+      <c r="C271" s="22" t="s">
+        <v>692</v>
+      </c>
+      <c r="D271" s="24" t="s">
+        <v>695</v>
+      </c>
+      <c r="E271" s="22"/>
+      <c r="F271" s="24"/>
+      <c r="G271" s="24"/>
+      <c r="H271" s="24"/>
+      <c r="I271" s="24"/>
+      <c r="J271" s="24"/>
+      <c r="K271" s="24"/>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A272" s="22"/>
+      <c r="B272" s="24"/>
+      <c r="C272" s="22"/>
+      <c r="D272" s="24"/>
+      <c r="E272" s="22"/>
+      <c r="F272" s="24"/>
+      <c r="G272" s="24"/>
+      <c r="H272" s="24"/>
+      <c r="I272" s="24"/>
+      <c r="J272" s="24"/>
+      <c r="K272" s="24"/>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A273" s="20"/>
+      <c r="B273" s="21"/>
+      <c r="C273" s="20"/>
+      <c r="D273" s="21"/>
+      <c r="E273" s="20"/>
+      <c r="F273" s="21"/>
+      <c r="G273" s="21"/>
+      <c r="H273" s="21"/>
+      <c r="I273" s="21"/>
+      <c r="J273" s="21"/>
+      <c r="K273" s="21"/>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C282" s="1" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C283" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="D283" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C284" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="D284" t="s">
         <v>519</v>
       </c>
     </row>
-    <row r="271" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C271" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="D271" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="272" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="C272" s="1" t="s">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C285" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="D272" t="s">
+      <c r="D285" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="273" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C273" s="1" t="s">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C286" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="D273" t="s">
+      <c r="D286" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="274" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C274" s="1" t="s">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C287" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="D274" t="s">
+      <c r="D287" t="s">
         <v>525</v>
       </c>
     </row>
-    <row r="275" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C275" s="1" t="s">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C288" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="D275" t="s">
+      <c r="D288" t="s">
         <v>527</v>
       </c>
     </row>
-    <row r="276" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C276" s="1" t="s">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C289" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="D276" t="s">
+      <c r="D289" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="277" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C277" s="1" t="s">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C290" s="1" t="s">
         <v>534</v>
       </c>
-      <c r="D277" t="s">
+      <c r="D290" t="s">
         <v>531</v>
       </c>
     </row>
-    <row r="278" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C278" s="1" t="s">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C291" s="1" t="s">
         <v>536</v>
       </c>
-      <c r="D278" t="s">
+      <c r="D291" t="s">
         <v>533</v>
       </c>
     </row>
-    <row r="279" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C279" s="1" t="s">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C292" s="1" t="s">
         <v>538</v>
       </c>
-      <c r="D279" t="s">
+      <c r="D292" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="280" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C280" s="1" t="s">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C293" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="D280" t="s">
+      <c r="D293" t="s">
         <v>537</v>
       </c>
     </row>
-    <row r="281" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C281" s="1" t="s">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C294" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="D281" t="s">
+      <c r="D294" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="282" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C282" s="1" t="s">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C295" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D295" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C296" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D296" t="s">
         <v>544</v>
       </c>
-      <c r="D282" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="283" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C283" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="D283" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="284" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C284" s="1" t="s">
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C297" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="D284" t="s">
+      <c r="D297" t="s">
         <v>546</v>
       </c>
     </row>
-    <row r="285" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C285" s="1" t="s">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C298" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="D285" t="s">
+      <c r="D298" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="286" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C286" s="1" t="s">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C299" s="1" t="s">
         <v>551</v>
       </c>
-      <c r="D286" t="s">
+      <c r="D299" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="287" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C287" s="1" t="s">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C300" s="1" t="s">
         <v>553</v>
       </c>
-      <c r="D287" t="s">
+      <c r="D300" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="288" spans="3:4" x14ac:dyDescent="0.35">
-      <c r="C288" s="1" t="s">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D301" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A302" s="26"/>
+      <c r="B302" s="25"/>
+      <c r="C302" s="26"/>
+      <c r="D302" s="25"/>
+      <c r="E302" s="26"/>
+      <c r="F302" s="25"/>
+      <c r="G302" s="25"/>
+      <c r="H302" s="25"/>
+      <c r="I302" s="25"/>
+      <c r="J302" s="25"/>
+      <c r="K302" s="25"/>
+    </row>
+    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A303" s="39">
+        <v>16</v>
+      </c>
+      <c r="B303" s="40" t="s">
+        <v>516</v>
+      </c>
+      <c r="C303" s="41" t="s">
+        <v>468</v>
+      </c>
+      <c r="D303" s="42" t="s">
+        <v>480</v>
+      </c>
+      <c r="E303" s="39" t="s">
+        <v>696</v>
+      </c>
+      <c r="F303" s="42" t="s">
+        <v>516</v>
+      </c>
+      <c r="G303" s="42"/>
+      <c r="H303" s="42"/>
+      <c r="I303" s="42"/>
+      <c r="J303" s="42"/>
+      <c r="K303" s="42"/>
+    </row>
+    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A304" s="39"/>
+      <c r="B304" s="42"/>
+      <c r="C304" s="41" t="s">
+        <v>469</v>
+      </c>
+      <c r="D304" s="42" t="s">
+        <v>481</v>
+      </c>
+      <c r="E304" s="39"/>
+      <c r="F304" s="42"/>
+      <c r="G304" s="42"/>
+      <c r="H304" s="42"/>
+      <c r="I304" s="42"/>
+      <c r="J304" s="42"/>
+      <c r="K304" s="42"/>
+    </row>
+    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A305" s="39"/>
+      <c r="B305" s="42"/>
+      <c r="C305" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="D305" s="42" t="s">
+        <v>482</v>
+      </c>
+      <c r="E305" s="39"/>
+      <c r="F305" s="42"/>
+      <c r="G305" s="42"/>
+      <c r="H305" s="42"/>
+      <c r="I305" s="42"/>
+      <c r="J305" s="42"/>
+      <c r="K305" s="42"/>
+    </row>
+    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A306" s="39"/>
+      <c r="B306" s="42"/>
+      <c r="C306" s="41" t="s">
+        <v>471</v>
+      </c>
+      <c r="D306" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="E306" s="39"/>
+      <c r="F306" s="42"/>
+      <c r="G306" s="42"/>
+      <c r="H306" s="42"/>
+      <c r="I306" s="42"/>
+      <c r="J306" s="42"/>
+      <c r="K306" s="42"/>
+    </row>
+    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A307" s="39"/>
+      <c r="B307" s="42"/>
+      <c r="C307" s="41" t="s">
+        <v>472</v>
+      </c>
+      <c r="D307" s="42" t="s">
+        <v>484</v>
+      </c>
+      <c r="E307" s="39"/>
+      <c r="F307" s="42"/>
+      <c r="G307" s="42"/>
+      <c r="H307" s="42"/>
+      <c r="I307" s="42"/>
+      <c r="J307" s="42"/>
+      <c r="K307" s="42"/>
+    </row>
+    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A308" s="39"/>
+      <c r="B308" s="42"/>
+      <c r="C308" s="41" t="s">
+        <v>473</v>
+      </c>
+      <c r="D308" s="42" t="s">
+        <v>485</v>
+      </c>
+      <c r="E308" s="39"/>
+      <c r="F308" s="42"/>
+      <c r="G308" s="42"/>
+      <c r="H308" s="42"/>
+      <c r="I308" s="42"/>
+      <c r="J308" s="42"/>
+      <c r="K308" s="42"/>
+    </row>
+    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A309" s="39"/>
+      <c r="B309" s="42"/>
+      <c r="C309" s="41" t="s">
+        <v>474</v>
+      </c>
+      <c r="D309" s="42" t="s">
+        <v>486</v>
+      </c>
+      <c r="E309" s="39"/>
+      <c r="F309" s="42"/>
+      <c r="G309" s="42"/>
+      <c r="H309" s="42"/>
+      <c r="I309" s="42"/>
+      <c r="J309" s="42"/>
+      <c r="K309" s="42"/>
+    </row>
+    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A310" s="39"/>
+      <c r="B310" s="42"/>
+      <c r="C310" s="41" t="s">
+        <v>475</v>
+      </c>
+      <c r="D310" s="42" t="s">
+        <v>487</v>
+      </c>
+      <c r="E310" s="39"/>
+      <c r="F310" s="42"/>
+      <c r="G310" s="42"/>
+      <c r="H310" s="42"/>
+      <c r="I310" s="42"/>
+      <c r="J310" s="42"/>
+      <c r="K310" s="42"/>
+    </row>
+    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A311" s="39"/>
+      <c r="B311" s="42"/>
+      <c r="C311" s="41" t="s">
+        <v>476</v>
+      </c>
+      <c r="D311" s="42" t="s">
+        <v>488</v>
+      </c>
+      <c r="E311" s="39"/>
+      <c r="F311" s="42"/>
+      <c r="G311" s="42"/>
+      <c r="H311" s="42"/>
+      <c r="I311" s="42"/>
+      <c r="J311" s="42"/>
+      <c r="K311" s="42"/>
+    </row>
+    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A312" s="39"/>
+      <c r="B312" s="42"/>
+      <c r="C312" s="41" t="s">
+        <v>477</v>
+      </c>
+      <c r="D312" s="42" t="s">
+        <v>490</v>
+      </c>
+      <c r="E312" s="39"/>
+      <c r="F312" s="42"/>
+      <c r="G312" s="42"/>
+      <c r="H312" s="42"/>
+      <c r="I312" s="42"/>
+      <c r="J312" s="42"/>
+      <c r="K312" s="42"/>
+    </row>
+    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A313" s="39"/>
+      <c r="B313" s="42"/>
+      <c r="C313" s="41" t="s">
+        <v>478</v>
+      </c>
+      <c r="D313" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="E313" s="39"/>
+      <c r="F313" s="42"/>
+      <c r="G313" s="42"/>
+      <c r="H313" s="42"/>
+      <c r="I313" s="42"/>
+      <c r="J313" s="42"/>
+      <c r="K313" s="42"/>
+    </row>
+    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A314" s="39"/>
+      <c r="B314" s="42"/>
+      <c r="C314" s="41" t="s">
+        <v>479</v>
+      </c>
+      <c r="D314" s="42" t="s">
+        <v>491</v>
+      </c>
+      <c r="E314" s="39"/>
+      <c r="F314" s="42"/>
+      <c r="G314" s="42"/>
+      <c r="H314" s="42"/>
+      <c r="I314" s="42"/>
+      <c r="J314" s="42"/>
+      <c r="K314" s="42"/>
+    </row>
+    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A315" s="39"/>
+      <c r="B315" s="42"/>
+      <c r="C315" s="41" t="s">
+        <v>503</v>
+      </c>
+      <c r="D315" s="42" t="s">
+        <v>492</v>
+      </c>
+      <c r="E315" s="39"/>
+      <c r="F315" s="42"/>
+      <c r="G315" s="42"/>
+      <c r="H315" s="42"/>
+      <c r="I315" s="42"/>
+      <c r="J315" s="42"/>
+      <c r="K315" s="42"/>
+    </row>
+    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A316" s="39"/>
+      <c r="B316" s="42"/>
+      <c r="C316" s="41" t="s">
+        <v>504</v>
+      </c>
+      <c r="D316" s="42" t="s">
+        <v>493</v>
+      </c>
+      <c r="E316" s="39"/>
+      <c r="F316" s="42"/>
+      <c r="G316" s="42"/>
+      <c r="H316" s="42"/>
+      <c r="I316" s="42"/>
+      <c r="J316" s="42"/>
+      <c r="K316" s="42"/>
+    </row>
+    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A317" s="39"/>
+      <c r="B317" s="42"/>
+      <c r="C317" s="41" t="s">
+        <v>505</v>
+      </c>
+      <c r="D317" s="42" t="s">
+        <v>494</v>
+      </c>
+      <c r="E317" s="39"/>
+      <c r="F317" s="42"/>
+      <c r="G317" s="42"/>
+      <c r="H317" s="42"/>
+      <c r="I317" s="42"/>
+      <c r="J317" s="42"/>
+      <c r="K317" s="42"/>
+    </row>
+    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A318" s="39"/>
+      <c r="B318" s="42"/>
+      <c r="C318" s="41" t="s">
+        <v>506</v>
+      </c>
+      <c r="D318" s="42" t="s">
+        <v>495</v>
+      </c>
+      <c r="E318" s="39"/>
+      <c r="F318" s="42"/>
+      <c r="G318" s="42"/>
+      <c r="H318" s="42"/>
+      <c r="I318" s="42"/>
+      <c r="J318" s="42"/>
+      <c r="K318" s="42"/>
+    </row>
+    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A319" s="39"/>
+      <c r="B319" s="42"/>
+      <c r="C319" s="41" t="s">
+        <v>507</v>
+      </c>
+      <c r="D319" s="42" t="s">
+        <v>496</v>
+      </c>
+      <c r="E319" s="39"/>
+      <c r="F319" s="42"/>
+      <c r="G319" s="42"/>
+      <c r="H319" s="42"/>
+      <c r="I319" s="42"/>
+      <c r="J319" s="42"/>
+      <c r="K319" s="42"/>
+    </row>
+    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A320" s="39"/>
+      <c r="B320" s="42"/>
+      <c r="C320" s="41" t="s">
+        <v>508</v>
+      </c>
+      <c r="D320" s="42" t="s">
+        <v>497</v>
+      </c>
+      <c r="E320" s="39"/>
+      <c r="F320" s="42"/>
+      <c r="G320" s="42"/>
+      <c r="H320" s="42"/>
+      <c r="I320" s="42"/>
+      <c r="J320" s="42"/>
+      <c r="K320" s="42"/>
+    </row>
+    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A321" s="39"/>
+      <c r="B321" s="42"/>
+      <c r="C321" s="41" t="s">
+        <v>509</v>
+      </c>
+      <c r="D321" s="42" t="s">
+        <v>498</v>
+      </c>
+      <c r="E321" s="39"/>
+      <c r="F321" s="42"/>
+      <c r="G321" s="42"/>
+      <c r="H321" s="42"/>
+      <c r="I321" s="42"/>
+      <c r="J321" s="42"/>
+      <c r="K321" s="42"/>
+    </row>
+    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A322" s="39"/>
+      <c r="B322" s="42"/>
+      <c r="C322" s="41" t="s">
+        <v>510</v>
+      </c>
+      <c r="D322" s="42" t="s">
+        <v>499</v>
+      </c>
+      <c r="E322" s="39"/>
+      <c r="F322" s="42"/>
+      <c r="G322" s="42"/>
+      <c r="H322" s="42"/>
+      <c r="I322" s="42"/>
+      <c r="J322" s="42"/>
+      <c r="K322" s="42"/>
+    </row>
+    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A323" s="39"/>
+      <c r="B323" s="42"/>
+      <c r="C323" s="41" t="s">
+        <v>511</v>
+      </c>
+      <c r="D323" s="42" t="s">
+        <v>500</v>
+      </c>
+      <c r="E323" s="39"/>
+      <c r="F323" s="42"/>
+      <c r="G323" s="42"/>
+      <c r="H323" s="42"/>
+      <c r="I323" s="42"/>
+      <c r="J323" s="42"/>
+      <c r="K323" s="42"/>
+    </row>
+    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A324" s="39"/>
+      <c r="B324" s="42"/>
+      <c r="C324" s="41" t="s">
+        <v>512</v>
+      </c>
+      <c r="D324" s="42" t="s">
+        <v>501</v>
+      </c>
+      <c r="E324" s="39"/>
+      <c r="F324" s="42"/>
+      <c r="G324" s="42"/>
+      <c r="H324" s="42"/>
+      <c r="I324" s="42"/>
+      <c r="J324" s="42"/>
+      <c r="K324" s="42"/>
+    </row>
+    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A325" s="39"/>
+      <c r="B325" s="42"/>
+      <c r="C325" s="41" t="s">
+        <v>513</v>
+      </c>
+      <c r="D325" s="42" t="s">
+        <v>502</v>
+      </c>
+      <c r="E325" s="39"/>
+      <c r="F325" s="42"/>
+      <c r="G325" s="42"/>
+      <c r="H325" s="42"/>
+      <c r="I325" s="42"/>
+      <c r="J325" s="42"/>
+      <c r="K325" s="42"/>
+    </row>
+    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A326" s="39"/>
+      <c r="B326" s="42"/>
+      <c r="C326" s="41" t="s">
+        <v>514</v>
+      </c>
+      <c r="D326" s="42" t="s">
+        <v>515</v>
+      </c>
+      <c r="E326" s="39"/>
+      <c r="F326" s="42"/>
+      <c r="G326" s="42"/>
+      <c r="H326" s="42"/>
+      <c r="I326" s="42"/>
+      <c r="J326" s="42"/>
+      <c r="K326" s="42"/>
+    </row>
+    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A327" s="26"/>
+      <c r="B327" s="25"/>
+      <c r="C327" s="26"/>
+      <c r="D327" s="25"/>
+      <c r="E327" s="26"/>
+      <c r="F327" s="25"/>
+      <c r="G327" s="25"/>
+      <c r="H327" s="25"/>
+      <c r="I327" s="25"/>
+      <c r="J327" s="25"/>
+      <c r="K327" s="25"/>
+    </row>
+    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A328" s="32"/>
+      <c r="B328" s="33" t="s">
         <v>555</v>
       </c>
-      <c r="D288" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D289" t="s">
+      <c r="C328" s="32" t="s">
         <v>556</v>
       </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A291" s="4"/>
-      <c r="B291" s="5" t="s">
-        <v>518</v>
-      </c>
-      <c r="C291" s="18" t="s">
-        <v>470</v>
-      </c>
-      <c r="E291" s="4"/>
-      <c r="F291" s="5"/>
-      <c r="G291" s="5"/>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A292" s="4"/>
-      <c r="B292" s="5"/>
-      <c r="C292" s="18" t="s">
-        <v>471</v>
-      </c>
-      <c r="D292" s="19" t="s">
-        <v>482</v>
-      </c>
-      <c r="E292" s="4"/>
-      <c r="F292" s="5"/>
-      <c r="G292" s="5"/>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A293" s="4"/>
-      <c r="B293" s="5"/>
-      <c r="C293" s="18" t="s">
-        <v>472</v>
-      </c>
-      <c r="D293" s="19" t="s">
-        <v>483</v>
-      </c>
-      <c r="E293" s="4"/>
-      <c r="F293" s="5"/>
-      <c r="G293" s="5"/>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A294" s="4"/>
-      <c r="B294" s="5"/>
-      <c r="C294" s="18" t="s">
-        <v>473</v>
-      </c>
-      <c r="D294" s="19" t="s">
-        <v>484</v>
-      </c>
-      <c r="E294" s="4"/>
-      <c r="F294" s="5"/>
-      <c r="G294" s="5"/>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A295" s="4"/>
-      <c r="B295" s="5"/>
-      <c r="C295" s="18" t="s">
-        <v>474</v>
-      </c>
-      <c r="D295" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="E295" s="4"/>
-      <c r="F295" s="5"/>
-      <c r="G295" s="5"/>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A296" s="4"/>
-      <c r="B296" s="5"/>
-      <c r="C296" s="18" t="s">
-        <v>475</v>
-      </c>
-      <c r="D296" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="E296" s="4"/>
-      <c r="F296" s="5"/>
-      <c r="G296" s="5"/>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A297" s="4"/>
-      <c r="B297" s="5"/>
-      <c r="C297" s="18" t="s">
-        <v>476</v>
-      </c>
-      <c r="D297" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="E297" s="4"/>
-      <c r="F297" s="5"/>
-      <c r="G297" s="5"/>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A298" s="4"/>
-      <c r="B298" s="5"/>
-      <c r="C298" s="18" t="s">
-        <v>477</v>
-      </c>
-      <c r="D298" s="19" t="s">
-        <v>488</v>
-      </c>
-      <c r="E298" s="4"/>
-      <c r="F298" s="5"/>
-      <c r="G298" s="5"/>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A299" s="4"/>
-      <c r="B299" s="5"/>
-      <c r="C299" s="18" t="s">
-        <v>478</v>
-      </c>
-      <c r="D299" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="E299" s="4"/>
-      <c r="F299" s="5"/>
-      <c r="G299" s="5"/>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A300" s="4"/>
-      <c r="B300" s="5"/>
-      <c r="C300" s="18" t="s">
-        <v>479</v>
-      </c>
-      <c r="D300" s="19" t="s">
-        <v>490</v>
-      </c>
-      <c r="E300" s="4"/>
-      <c r="F300" s="5"/>
-      <c r="G300" s="5"/>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A301" s="4"/>
-      <c r="B301" s="5"/>
-      <c r="C301" s="18" t="s">
-        <v>480</v>
-      </c>
-      <c r="D301" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="E301" s="4"/>
-      <c r="F301" s="5"/>
-      <c r="G301" s="5"/>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A302" s="4"/>
-      <c r="B302" s="5"/>
-      <c r="C302" s="18" t="s">
-        <v>481</v>
-      </c>
-      <c r="D302" s="19" t="s">
-        <v>491</v>
-      </c>
-      <c r="E302" s="4"/>
-      <c r="F302" s="5"/>
-      <c r="G302" s="5"/>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A303" s="4"/>
-      <c r="B303" s="5"/>
-      <c r="C303" s="18" t="s">
-        <v>505</v>
-      </c>
-      <c r="D303" s="19" t="s">
-        <v>493</v>
-      </c>
-      <c r="E303" s="4"/>
-      <c r="F303" s="5"/>
-      <c r="G303" s="5"/>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A304" s="4"/>
-      <c r="B304" s="5"/>
-      <c r="C304" s="18" t="s">
-        <v>506</v>
-      </c>
-      <c r="D304" s="19" t="s">
-        <v>494</v>
-      </c>
-      <c r="E304" s="4"/>
-      <c r="F304" s="5"/>
-      <c r="G304" s="5"/>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A305" s="4"/>
-      <c r="B305" s="5"/>
-      <c r="C305" s="18" t="s">
-        <v>507</v>
-      </c>
-      <c r="D305" s="19" t="s">
-        <v>495</v>
-      </c>
-      <c r="E305" s="4"/>
-      <c r="F305" s="5"/>
-      <c r="G305" s="5"/>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A306" s="4"/>
-      <c r="B306" s="5"/>
-      <c r="C306" s="18" t="s">
-        <v>508</v>
-      </c>
-      <c r="D306" s="19" t="s">
-        <v>496</v>
-      </c>
-      <c r="E306" s="4"/>
-      <c r="F306" s="5"/>
-      <c r="G306" s="5"/>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A307" s="4"/>
-      <c r="B307" s="5"/>
-      <c r="C307" s="18" t="s">
-        <v>509</v>
-      </c>
-      <c r="D307" s="19" t="s">
-        <v>497</v>
-      </c>
-      <c r="E307" s="4"/>
-      <c r="F307" s="5"/>
-      <c r="G307" s="5"/>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A308" s="4"/>
-      <c r="B308" s="5"/>
-      <c r="C308" s="18" t="s">
-        <v>510</v>
-      </c>
-      <c r="D308" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="E308" s="4"/>
-      <c r="F308" s="5"/>
-      <c r="G308" s="5"/>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A309" s="4"/>
-      <c r="B309" s="5"/>
-      <c r="C309" s="18" t="s">
-        <v>511</v>
-      </c>
-      <c r="D309" s="19" t="s">
-        <v>499</v>
-      </c>
-      <c r="E309" s="4"/>
-      <c r="F309" s="5"/>
-      <c r="G309" s="5"/>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A310" s="4"/>
-      <c r="B310" s="5"/>
-      <c r="C310" s="18" t="s">
-        <v>512</v>
-      </c>
-      <c r="D310" s="19" t="s">
-        <v>500</v>
-      </c>
-      <c r="E310" s="4"/>
-      <c r="F310" s="5"/>
-      <c r="G310" s="5"/>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A311" s="4"/>
-      <c r="B311" s="5"/>
-      <c r="C311" s="18" t="s">
-        <v>513</v>
-      </c>
-      <c r="D311" s="19" t="s">
-        <v>501</v>
-      </c>
-      <c r="E311" s="4"/>
-      <c r="F311" s="5"/>
-      <c r="G311" s="5"/>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A312" s="4"/>
-      <c r="B312" s="5"/>
-      <c r="C312" s="18" t="s">
-        <v>514</v>
-      </c>
-      <c r="D312" s="19" t="s">
-        <v>502</v>
-      </c>
-      <c r="E312" s="4"/>
-      <c r="F312" s="5"/>
-      <c r="G312" s="5"/>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A313" s="4"/>
-      <c r="B313" s="5"/>
-      <c r="C313" s="18" t="s">
-        <v>515</v>
-      </c>
-      <c r="D313" s="19" t="s">
-        <v>503</v>
-      </c>
-      <c r="E313" s="4"/>
-      <c r="F313" s="5"/>
-      <c r="G313" s="5"/>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A314" s="4"/>
-      <c r="B314" s="5"/>
-      <c r="C314" s="18" t="s">
-        <v>516</v>
-      </c>
-      <c r="D314" s="19" t="s">
-        <v>504</v>
-      </c>
-      <c r="E314" s="4"/>
-      <c r="F314" s="5"/>
-      <c r="G314" s="5"/>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D315" s="19" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A316" s="4"/>
-      <c r="B316" s="5" t="s">
+      <c r="D328" s="38" t="s">
         <v>557</v>
       </c>
-      <c r="C316" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="E316" s="4"/>
-      <c r="F316" s="5"/>
-      <c r="G316" s="5"/>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A317" s="4"/>
-      <c r="B317" s="5"/>
-      <c r="C317" s="4" t="s">
-        <v>560</v>
-      </c>
-      <c r="D317" s="19" t="s">
-        <v>559</v>
-      </c>
-      <c r="E317" s="4"/>
-      <c r="F317" s="5"/>
-      <c r="G317" s="5"/>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D318" s="19" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A319" s="4"/>
-      <c r="B319" s="5" t="s">
-        <v>568</v>
-      </c>
-      <c r="C319" s="4" t="s">
-        <v>562</v>
-      </c>
-      <c r="E319" s="4"/>
-      <c r="F319" s="5"/>
-      <c r="G319" s="5"/>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A320" s="4"/>
-      <c r="B320" s="5"/>
-      <c r="C320" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="D320" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="E320" s="4"/>
-      <c r="F320" s="5"/>
-      <c r="G320" s="5"/>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A321" s="4"/>
-      <c r="B321" s="5"/>
-      <c r="C321" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="D321" s="16" t="s">
-        <v>563</v>
-      </c>
-      <c r="E321" s="4"/>
-      <c r="F321" s="5"/>
-      <c r="G321" s="5"/>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A322" s="4"/>
-      <c r="B322" s="5"/>
-      <c r="C322" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="D322" s="16" t="s">
-        <v>564</v>
-      </c>
-      <c r="E322" s="4"/>
-      <c r="F322" s="5"/>
-      <c r="G322" s="5"/>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A323" s="4"/>
-      <c r="B323" s="5"/>
-      <c r="C323" s="4" t="s">
-        <v>566</v>
-      </c>
-      <c r="D323" s="16" t="s">
-        <v>565</v>
-      </c>
-      <c r="E323" s="4"/>
-      <c r="F323" s="5"/>
-      <c r="G323" s="5"/>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A324" s="4"/>
-      <c r="B324" s="5"/>
-      <c r="C324" s="4"/>
-      <c r="D324" s="16" t="s">
-        <v>566</v>
-      </c>
-      <c r="E324" s="4"/>
-      <c r="F324" s="5"/>
-      <c r="G324" s="5"/>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A325" s="4"/>
-      <c r="B325" s="5" t="s">
-        <v>569</v>
-      </c>
-      <c r="C325" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="D325" s="5"/>
-      <c r="E325" s="4"/>
-      <c r="F325" s="5" t="s">
-        <v>580</v>
-      </c>
-      <c r="G325" s="5"/>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A326" s="4"/>
-      <c r="B326" s="5"/>
-      <c r="C326" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="D326" s="16" t="s">
-        <v>583</v>
-      </c>
-      <c r="E326" s="4"/>
-      <c r="F326" s="5" t="s">
-        <v>581</v>
-      </c>
-      <c r="G326" s="5"/>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A327" s="4"/>
-      <c r="B327" s="5"/>
-      <c r="C327" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="D327" s="16" t="s">
-        <v>584</v>
-      </c>
-      <c r="E327" s="4"/>
-      <c r="F327" s="5" t="s">
-        <v>582</v>
-      </c>
-      <c r="G327" s="5"/>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A328" s="4"/>
-      <c r="B328" s="5"/>
-      <c r="C328" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="D328" s="16" t="s">
-        <v>585</v>
-      </c>
-      <c r="E328" s="4"/>
-      <c r="F328" s="5" t="s">
-        <v>586</v>
-      </c>
-      <c r="G328" s="5"/>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E328" s="32"/>
+      <c r="F328" s="33"/>
+      <c r="G328" s="33"/>
+    </row>
+    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A329" s="4"/>
       <c r="B329" s="5"/>
       <c r="C329" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="D329" s="16" t="s">
-        <v>587</v>
+        <v>558</v>
+      </c>
+      <c r="D329" s="18" t="s">
+        <v>559</v>
       </c>
       <c r="E329" s="4"/>
       <c r="F329" s="5"/>
       <c r="G329" s="5"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A330" s="4"/>
-      <c r="B330" s="5"/>
-      <c r="C330" s="4"/>
-      <c r="D330" s="16" t="s">
-        <v>573</v>
-      </c>
-      <c r="E330" s="4"/>
-      <c r="F330" s="5"/>
-      <c r="G330" s="5"/>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A331" s="4"/>
       <c r="B331" s="5" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="D331" s="5"/>
+        <v>560</v>
+      </c>
+      <c r="D331" s="16" t="s">
+        <v>560</v>
+      </c>
       <c r="E331" s="4"/>
       <c r="F331" s="5"/>
       <c r="G331" s="5"/>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A332" s="4"/>
       <c r="B332" s="5"/>
       <c r="C332" s="4" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="D332" s="16" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="E332" s="4"/>
       <c r="F332" s="5"/>
       <c r="G332" s="5"/>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A333" s="4"/>
       <c r="B333" s="5"/>
       <c r="C333" s="4" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="D333" s="16" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="E333" s="4"/>
       <c r="F333" s="5"/>
       <c r="G333" s="5"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A334" s="4"/>
       <c r="B334" s="5"/>
       <c r="C334" s="4" t="s">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="D334" s="16" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="E334" s="4"/>
       <c r="F334" s="5"/>
       <c r="G334" s="5"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A335" s="4"/>
       <c r="B335" s="5"/>
       <c r="C335" s="4" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="D335" s="16" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="E335" s="4"/>
       <c r="F335" s="5"/>
       <c r="G335" s="5"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D336" s="16" t="s">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A336" s="4"/>
+      <c r="B336" s="5"/>
+      <c r="C336" s="4"/>
+      <c r="D336" s="5"/>
+      <c r="E336" s="4"/>
+      <c r="F336" s="5"/>
+      <c r="G336" s="5"/>
+    </row>
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A337" s="4"/>
+      <c r="B337" s="5" t="s">
+        <v>567</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="D337" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="E337" s="4"/>
+      <c r="F337" s="5" t="s">
+        <v>578</v>
+      </c>
+      <c r="G337" s="5"/>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A338" s="4"/>
+      <c r="B338" s="5"/>
+      <c r="C338" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="D338" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="E338" s="4"/>
+      <c r="F338" s="5" t="s">
         <v>579</v>
       </c>
+      <c r="G338" s="5"/>
+    </row>
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A339" s="4"/>
+      <c r="B339" s="5"/>
+      <c r="C339" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="D339" s="16" t="s">
+        <v>583</v>
+      </c>
+      <c r="E339" s="4"/>
+      <c r="F339" s="5" t="s">
+        <v>580</v>
+      </c>
+      <c r="G339" s="5"/>
+    </row>
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A340" s="4"/>
+      <c r="B340" s="5"/>
+      <c r="C340" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="D340" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="E340" s="4"/>
+      <c r="F340" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="G340" s="5"/>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A341" s="4"/>
+      <c r="B341" s="5"/>
+      <c r="C341" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="D341" s="16" t="s">
+        <v>571</v>
+      </c>
+      <c r="E341" s="4"/>
+      <c r="F341" s="5"/>
+      <c r="G341" s="5"/>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A342" s="4"/>
+      <c r="B342" s="5"/>
+      <c r="C342" s="4"/>
+      <c r="D342" s="5"/>
+      <c r="E342" s="4"/>
+      <c r="F342" s="5"/>
+      <c r="G342" s="5"/>
+    </row>
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A343" s="4"/>
+      <c r="B343" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="D343" s="16" t="s">
+        <v>573</v>
+      </c>
+      <c r="E343" s="4"/>
+      <c r="F343" s="5"/>
+      <c r="G343" s="5"/>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A344" s="4"/>
+      <c r="B344" s="5"/>
+      <c r="C344" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="D344" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="E344" s="4"/>
+      <c r="F344" s="5"/>
+      <c r="G344" s="5"/>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A345" s="4"/>
+      <c r="B345" s="5"/>
+      <c r="C345" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="D345" s="16" t="s">
+        <v>575</v>
+      </c>
+      <c r="E345" s="4"/>
+      <c r="F345" s="5"/>
+      <c r="G345" s="5"/>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A346" s="4"/>
+      <c r="B346" s="5"/>
+      <c r="C346" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="D346" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="E346" s="4"/>
+      <c r="F346" s="5"/>
+      <c r="G346" s="5"/>
+    </row>
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A347" s="4"/>
+      <c r="B347" s="5"/>
+      <c r="C347" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="D347" s="16" t="s">
+        <v>577</v>
+      </c>
+      <c r="E347" s="4"/>
+      <c r="F347" s="5"/>
+      <c r="G347" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -6457,22 +7123,22 @@
   <sheetData>
     <row r="1" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" s="11" t="s">
         <v>190</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
@@ -6484,25 +7150,25 @@
       <c r="F2" s="11"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="N2" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>256</v>
-      </c>
       <c r="O2" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
@@ -6514,25 +7180,25 @@
       <c r="F3" s="11"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>254</v>
-      </c>
       <c r="L3" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -6544,83 +7210,83 @@
       <c r="F4" s="5"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="M4" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="4"/>
       <c r="F5" s="5"/>
       <c r="H5" s="12" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I5" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K5" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J5" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L5" s="13"/>
       <c r="M5" s="13"/>
       <c r="N5" s="13"/>
       <c r="O5" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>187</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>188</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="4"/>
       <c r="F6" s="5"/>
       <c r="H6" s="12" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I6" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K6" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J6" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L6" s="13"/>
       <c r="M6" s="13"/>
@@ -6629,278 +7295,278 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="4"/>
       <c r="F7" s="5"/>
       <c r="H7" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I7" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K7" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L7" s="13"/>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F8" s="5"/>
       <c r="H8" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I8" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K8" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J8" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K8" s="15" t="s">
+      <c r="L8" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M8" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="N8" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O8" s="12"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="F9" s="5"/>
       <c r="H9" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="I9" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K9" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J9" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K9" s="15" t="s">
+      <c r="L9" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M9" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="N9" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N9" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O9" s="12"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E10" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F10" s="5"/>
       <c r="H10" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I10" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K10" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J10" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K10" s="15" t="s">
+      <c r="L10" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M10" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="N10" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N10" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O10" s="12"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D11" s="5"/>
       <c r="E11" s="4"/>
       <c r="F11" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H11" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I11" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K11" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="L11" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="K11" s="15" t="s">
+      <c r="M11" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L11" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="M11" s="15" t="s">
+      <c r="N11" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O11" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="N11" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O11" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F12" s="5"/>
       <c r="H12" s="12" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I12" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K12" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J12" s="15" t="s">
+      <c r="L12" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M12" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N12" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O12" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="K12" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="L12" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N12" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O12" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E13" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F13" s="5"/>
       <c r="H13" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I13" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K13" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="L13" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M13" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N13" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O13" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="K13" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="L13" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="M13" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N13" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O13" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -6921,25 +7587,25 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D15" s="5"/>
       <c r="E15" s="4"/>
       <c r="F15" s="5"/>
       <c r="H15" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K15" s="13"/>
       <c r="L15" s="13"/>
@@ -6949,115 +7615,115 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E16" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F16" s="5"/>
       <c r="H16" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K16" s="13"/>
       <c r="L16" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M16" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N16" s="13"/>
       <c r="O16" s="12"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F17" s="5"/>
       <c r="H17" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K17" s="13"/>
       <c r="L17" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M17" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N17" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="M17" s="15" t="s">
+      <c r="O17" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="N17" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O17" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F18" s="5"/>
       <c r="H18" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I18" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J18" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K18" s="13"/>
       <c r="L18" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M18" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N18" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M18" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N18" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O18" s="12"/>
     </row>
@@ -7079,114 +7745,114 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I20" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L20" s="13"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
       <c r="O20" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H21" s="12" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="I21" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J21" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K21" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J21" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K21" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L21" s="13"/>
       <c r="M21" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N21" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O21" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H22" s="12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="I22" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J22" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K22" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J22" s="15" t="s">
+      <c r="L22" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="K22" s="15" t="s">
+      <c r="M22" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L22" s="12" t="s">
+      <c r="N22" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O22" s="12" t="s">
         <v>260</v>
-      </c>
-      <c r="M22" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N22" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -7223,28 +7889,28 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="4"/>
       <c r="F25" s="5"/>
       <c r="H25" s="12" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I25" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J25" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K25" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J25" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K25" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L25" s="13"/>
       <c r="M25" s="13"/>
@@ -7253,28 +7919,28 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="4"/>
       <c r="F26" s="5"/>
       <c r="H26" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I26" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J26" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K26" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J26" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K26" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L26" s="13"/>
       <c r="M26" s="13"/>
@@ -7283,216 +7949,216 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="4"/>
       <c r="F27" s="5"/>
       <c r="H27" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I27" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J27" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K27" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="J27" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K27" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="L27" s="13"/>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
       <c r="O27" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E28" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F28" s="5"/>
       <c r="H28" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I28" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J28" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K28" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J28" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K28" s="15" t="s">
+      <c r="L28" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M28" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L28" s="15" t="s">
+      <c r="N28" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M28" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N28" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O28" s="12"/>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E29" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F29" s="5"/>
       <c r="H29" s="12" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I29" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J29" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K29" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J29" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K29" s="15" t="s">
+      <c r="L29" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M29" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L29" s="15" t="s">
+      <c r="N29" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M29" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N29" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O29" s="12"/>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D30" s="5"/>
       <c r="E30" s="4"/>
       <c r="F30" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H30" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I30" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J30" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K30" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J30" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K30" s="15" t="s">
+      <c r="L30" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M30" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L30" s="15" t="s">
+      <c r="N30" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M30" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N30" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O30" s="12"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E31" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F31" s="5"/>
       <c r="H31" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I31" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J31" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K31" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J31" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="K31" s="15" t="s">
+      <c r="L31" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M31" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L31" s="15" t="s">
+      <c r="N31" s="15" t="s">
         <v>257</v>
-      </c>
-      <c r="M31" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N31" s="15" t="s">
-        <v>258</v>
       </c>
       <c r="O31" s="12"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E32" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F32" s="5"/>
       <c r="G32" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H32" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I32" s="4"/>
       <c r="J32" s="4"/>
@@ -7504,250 +8170,250 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E33" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F33" s="5"/>
       <c r="H33" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I33" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J33" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K33" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J33" s="15" t="s">
+      <c r="L33" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N33" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O33" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="K33" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="L33" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="M33" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N33" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O33" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E34" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F34" s="5"/>
       <c r="H34" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I34" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J34" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K34" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J34" s="15" t="s">
+      <c r="L34" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N34" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O34" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="K34" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="L34" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="M34" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N34" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O34" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E35" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F35" s="5"/>
       <c r="H35" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I35" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J35" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K35" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J35" s="15" t="s">
+      <c r="L35" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N35" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O35" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="K35" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="L35" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="M35" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N35" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O35" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E36" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F36" s="5"/>
       <c r="H36" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I36" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J36" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K36" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J36" s="15" t="s">
+      <c r="L36" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="N36" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O36" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="K36" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="L36" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="M36" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="N36" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O36" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="4"/>
       <c r="F37" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I37" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K37" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J37" s="15" t="s">
+      <c r="L37" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="K37" s="15" t="s">
+      <c r="M37" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L37" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="M37" s="15" t="s">
+      <c r="N37" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O37" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="N37" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="4"/>
       <c r="F38" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I38" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="K38" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="J38" s="15" t="s">
+      <c r="L38" s="12" t="s">
         <v>259</v>
       </c>
-      <c r="K38" s="15" t="s">
+      <c r="M38" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="L38" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="M38" s="15" t="s">
+      <c r="N38" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="O38" s="12" t="s">
         <v>259</v>
-      </c>
-      <c r="N38" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="O38" s="12" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
@@ -7768,25 +8434,25 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="4"/>
       <c r="F40" s="5"/>
       <c r="H40" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J40" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -7796,97 +8462,97 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E41" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F41" s="5"/>
       <c r="H41" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I41" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J41" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M41" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N41" s="4"/>
       <c r="O41" s="5"/>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E42" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J42" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="M42" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="N42" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="M42" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="N42" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="O42" s="5"/>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E43" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F43" s="5"/>
       <c r="H43" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="I43" s="4"/>
       <c r="J43" s="4"/>
@@ -7898,23 +8564,23 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E44" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F44" s="5"/>
       <c r="H44" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I44" s="4"/>
       <c r="J44" s="4"/>
@@ -7926,25 +8592,25 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E45" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I45" s="4"/>
       <c r="J45" s="4"/>
@@ -7964,13 +8630,13 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D47" s="5"/>
       <c r="E47" s="4"/>
@@ -7978,163 +8644,163 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="4"/>
       <c r="F48" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E49" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F49" s="5"/>
       <c r="H49" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J49" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="M49" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="N49" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="M49" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="N49" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="O49" s="5"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E50" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F50" s="5"/>
       <c r="H50" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J50" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="14" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M50" s="14" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N50" s="4"/>
       <c r="O50" s="5"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="4"/>
       <c r="F51" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D52" s="5"/>
       <c r="E52" s="4"/>
       <c r="F52" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H52" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I52" s="14" t="s">
+        <v>256</v>
+      </c>
+      <c r="J52" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="K52" s="14" t="s">
         <v>257</v>
-      </c>
-      <c r="J52" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="K52" s="14" t="s">
-        <v>258</v>
       </c>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E53" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F53" s="5"/>
       <c r="H53" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
@@ -8146,23 +8812,23 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>198</v>
-      </c>
       <c r="E54" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F54" s="5"/>
       <c r="H54" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
@@ -8174,21 +8840,21 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D55" s="5"/>
       <c r="E55" s="4"/>
       <c r="F55" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
@@ -8206,7 +8872,7 @@
       <c r="E56" s="4"/>
       <c r="F56" s="5"/>
       <c r="H56" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
@@ -8218,7 +8884,7 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="H57" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
@@ -8230,10 +8896,10 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H58" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="I58" s="4"/>
       <c r="J58" s="4"/>
@@ -8245,10 +8911,10 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
@@ -8260,7 +8926,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="H60" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I60" s="4"/>
       <c r="J60" s="4"/>
